--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Nada Fucelová, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Nada Fucelová, Robert Babuška </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Antonín Miller, Petr Kadera </t>
+          <t xml:space="preserve">Jiří Kubalík, Antonín Miller, Petr Kadera </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Michael Rawson, Stephan Schulz </t>
+          <t xml:space="preserve">Mikoláš Janota, Michael Rawson, Stephan Schulz </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Leroy Chew, Tomáš Peitl </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nikhil Sethi, Max Lodel, Laura Ferranti, Robert Babuska, Javier Alonso-Mora </t>
+          <t xml:space="preserve">Nikhil Sethi, Max Lodel, Laura Ferranti, Robert Babuška, Javier Alonso-Mora </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nikolai Antonov, Premysl Sucha, Mikolás Janota, Jan Hula </t>
+          <t xml:space="preserve">Nikolai Antonov, Premysl Sucha, Mikoláš Janota, Jan Hůla </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Michael Rawson, Stephan Schulz </t>
+          <t xml:space="preserve">Mikoláš Janota, Michael Rawson, Stephan Schulz </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan Ratschan, Anggha Nugraha, Mikolás Janota, Marek Danco </t>
+          <t xml:space="preserve">Stefan Ratschan, Anggha Nugraha, Mikoláš Janota, Marek Dančo </t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Mikolás Janota, Miroslav Olsák, Martin Suda </t>
+          <t xml:space="preserve">Leroy Chew, Mikoláš Janota, Miroslav Olšák, Martin Suda </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Mirek Olsák </t>
+          <t xml:space="preserve">Mikoláš Janota, Mirek Olšák </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max Lodel, Nils Wilde, Robert Babuska, Javier Alonso-Mora </t>
+          <t xml:space="preserve">Max Lodel, Nils Wilde, Robert Babuška, Javier Alonso-Mora </t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qiqi Jason Gu, Mikolás Janota </t>
+          <t xml:space="preserve">Qiqi Jason Gu, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Adamczyk, Tomás Filip, Martin Pavlícek, Petr Sosík </t>
+          <t xml:space="preserve">Jan Hůla, David Adamczyk, Tomáš Filip, Martin Pavlícek, Petr Sosík </t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Warchocki, Xi Wang, Jonas Kulhanek, Jan van Gemert </t>
+          <t xml:space="preserve">Jan Warchocki, Xi Wang, Jonáš Kulhánek, Jan van Gemert </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav David, Karla Stépánová, Robert Babuska </t>
+          <t xml:space="preserve">Miroslav David, Karla Stépánová, Robert Babuška </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1111,7 +1111,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Leroy Chew, Tomáš Peitl </t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nikhil Sethi, Max Lodel, Laura Ferranti, Robert Babuska, Javier Alonso-Mora </t>
+          <t xml:space="preserve">Nikhil Sethi, Max Lodel, Laura Ferranti, Robert Babuška, Javier Alonso-Mora </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Po-Nien Kung, Linfeng Song, Dawsen Hwang, Jinsung Yoon, Chun-Liang Li, Simone Severini, Mirek Olsák, Edward Lockhart, Quoc V. Le, Burak Gokturk, Thang Luong, Tomas Pfister, Nanyun Peng </t>
+          <t xml:space="preserve">Po-Nien Kung, Linfeng Song, Dawsen Hwang, Jinsung Yoon, Chun-Liang Li, Simone Severini, Mirek Olšák, Edward Lockhart, Quoc V. Le, Burak Gokturk, Thang Luong, Tomas Pfister, Nanyun Peng </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marek Danco, Karel Chvalovský, Mikolás Janota </t>
+          <t xml:space="preserve">Marek Dančo, Karel Chvalovský, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, William Klieber, João Marques-Silva, Edmund M. Clarke </t>
+          <t xml:space="preserve">Mikoláš Janota, William Klieber, João Marques-Silva, Edmund M. Clarke </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Mikolás Janota, Jelle Piepenbrock, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Mikoláš Janota, Jelle Piepenbrock, Josef Urban </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Mojzísek, Jan Hula, Ziwei Li, Ziyu Zhou, Mikolás Janota </t>
+          <t xml:space="preserve">David Mojzísek, Jan Hůla, Ziwei Li, Ziyu Zhou, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonáš Kulhánek </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marek Danco, Mikolás Janota, Michael Codish, João Jorge Araújo </t>
+          <t xml:space="preserve">Marek Dančo, Mikoláš Janota, Michael Codish, João Jorge Araújo </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Markus Kirchweger, Tomás Peitl, Stefan Szeider </t>
+          <t xml:space="preserve">Mikoláš Janota, Markus Kirchweger, Tomáš Peitl, Stefan Szeider </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco M. Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco M. Manquinho </t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Karel Chvalovský, Mikolás Janota, Mirek Olsák, Stefan Ratschan </t>
+          <t xml:space="preserve">Chad E. Brown, Karel Chvalovský, Mikoláš Janota, Mirek Olšák, Stefan Ratschan </t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Codish, Mikolás Janota </t>
+          <t xml:space="preserve">Michael Codish, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Codish, Mikolás Janota </t>
+          <t xml:space="preserve">Michael Codish, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Robert Babuška </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jan Ackermann, Jonáš Kulhánek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1921,7 +1921,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska </t>
+          <t xml:space="preserve">Robert Babuška </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Balyo, Roman Barták, Lukás Chrpa, Michal Cervenka, Filip Dvorák, Stephan Gocht, Lukás Lipcák, Viktor Macek, Dominik Rohácek, Josef Ryzí, Martin Suda, Dominik Safránek, Slavomír Svancár, G. Michael Youngblood </t>
+          <t xml:space="preserve">Tomáš Balyo, Roman Barták, Lukás Chrpa, Michal Cervenka, Filip Dvorák, Stephan Gocht, Lukás Lipcák, Viktor Macek, Dominik Rohácek, Josef Ryzí, Martin Suda, Dominik Safránek, Slavomír Svancár, G. Michael Youngblood </t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liao Zhang, Fabian Mitterwallner, Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Liao Zhang, Fabian Mitterwallner, Jan Jakubův, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2041,7 +2041,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hyner, Jan Mrógala, Jan Hula </t>
+          <t xml:space="preserve">Petr Hyner, Jan Mrógala, Jan Hůla </t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hyner, Jan Mrógala, Krystof Krmaschek, Jan Hula </t>
+          <t xml:space="preserve">Petr Hyner, Jan Mrógala, Krystof Krmaschek, Jan Hůla </t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jochen Hoenicke, Mikolás Janota, Aina Niemetz, Sophie Tourret </t>
+          <t xml:space="preserve">Jochen Hoenicke, Mikoláš Janota, Aina Niemetz, Sophie Tourret </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marek Danco, Petra Hozzová, Mikolás Janota </t>
+          <t xml:space="preserve">Marek Dančo, Petra Hozzová, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2311,7 +2311,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Mikolás Janota </t>
+          <t xml:space="preserve">Jan Jakubův, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Leroy Chew, Tomáš Peitl </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2371,7 +2371,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madalina Erascu, Mikolás Janota </t>
+          <t xml:space="preserve">Madalina Erascu, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2581,7 +2581,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaroslav Pazout, Milan Nemy, Jakub Mikes, Jan Jirman, Jan Kubr, Eliska Niebauerová, Miroslav Macík, Michal Pech, Michal Stajnrt, Jakub Vanek, Petr Waldauf, Vaclav Zvonícek, Lenka Vyslouzilova, Robert Babuska, Frantisek Duska </t>
+          <t xml:space="preserve">Jaroslav Pazout, Milan Nemy, Jakub Mikes, Jan Jirman, Jan Kubr, Eliska Niebauerová, Miroslav Macík, Michal Pech, Michal Stajnrt, Jakub Vanek, Petr Waldauf, Vaclav Zvonícek, Lenka Vyslouzilova, Robert Babuška, Frantisek Duska </t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Choiwah Chow, Mikolás Janota, João Araújo </t>
+          <t xml:space="preserve">Choiwah Chow, Mikoláš Janota, João Araújo </t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2641,7 +2641,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Choiwah Chow, João Araújo, Michael Codish, Petr Vojtechovský </t>
+          <t xml:space="preserve">Mikoláš Janota, Choiwah Chow, João Araújo, Michael Codish, Petr Vojtechovský </t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2671,7 +2671,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelle Piepenbrock, Mikolás Janota, Jan Jakubuv </t>
+          <t xml:space="preserve">Jelle Piepenbrock, Mikoláš Janota, Jan Jakubův </t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang Nguyen, Marcelo Menegali, Junehyuk Jung, Vikas Verma, Quoc V. Le, Thang Luong </t>
+          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olšák, Xiaomeng Yang, Hoang Nguyen, Marcelo Menegali, Junehyuk Jung, Vikas Verma, Quoc V. Le, Thang Luong </t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2731,7 +2731,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhaoting Li, Rodrigo Pérez-Dattari, Robert Babuska, Cosimo Della Santina, Jens Kober </t>
+          <t xml:space="preserve">Zhaoting Li, Rodrigo Pérez-Dattari, Robert Babuška, Cosimo Della Santina, Jens Kober </t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Codish, Mikolás Janota </t>
+          <t xml:space="preserve">Michael Codish, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marek Danco, Mikolás Janota, Michael Codish, João Araújo </t>
+          <t xml:space="preserve">Marek Dančo, Mikoláš Janota, Michael Codish, João Araújo </t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2851,7 +2851,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Markus Kirchweger, Tomás Peitl, Stefan Szeider </t>
+          <t xml:space="preserve">Mikoláš Janota, Markus Kirchweger, Tomáš Peitl, Stefan Szeider </t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
+          <t xml:space="preserve">Václav Jirkovský, Jiří Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Bartosz Piotrowski, Karel Chvalovský </t>
+          <t xml:space="preserve">Mikoláš Janota, Bartosz Piotrowski, Karel Chvalovský </t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3031,7 +3031,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Mojzísek, Jan Hula, Ziwei Li, Ziyu Zhou, Mikolás Janota </t>
+          <t xml:space="preserve">David Mojzísek, Jan Hůla, Ziwei Li, Ziyu Zhou, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Mojzísek, Jirí Janecek, David Herel, Mikolás Janota </t>
+          <t xml:space="preserve">Jan Hůla, David Mojzísek, Jiří Janecek, David Herel, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Karel Chvalovský, Mikolás Janota, Mirek Olsák, Stefan Ratschan </t>
+          <t xml:space="preserve">Chad E. Brown, Karel Chvalovský, Mikoláš Janota, Mirek Olšák, Stefan Ratschan </t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Robert Babuška </t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3211,7 +3211,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Leroy Chew, Tomáš Peitl </t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3271,7 +3271,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Codish, Mikolás Janota </t>
+          <t xml:space="preserve">Michael Codish, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3361,7 +3361,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jan Ackermann, Jonáš Kulhánek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marek Danco, Petra Hozzová, Mikolás Janota </t>
+          <t xml:space="preserve">Marek Dančo, Petra Hozzová, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3481,7 +3481,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonáš Kulhánek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3541,7 +3541,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Benders, Johannes Köhler, Robert Babuska, Javier Alonso-Mora, Laura Ferranti </t>
+          <t xml:space="preserve">Dennis Benders, Johannes Köhler, Robert Babuška, Javier Alonso-Mora, Laura Ferranti </t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nikolai Antonov, Premysl Sucha, Mikolás Janota, Jan Hula </t>
+          <t xml:space="preserve">Nikolai Antonov, Premysl Sucha, Mikoláš Janota, Jan Hůla </t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3631,7 +3631,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Mikolás Janota </t>
+          <t xml:space="preserve">Jan Jakubův, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3871,7 +3871,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Marta Kwiatkowska, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Marta Kwiatkowska, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3901,7 +3901,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Leroy Chew, Tomáš Peitl </t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pavlína Koutecká, Premysl Sucha, Jan Hula, Broos Maenhout </t>
+          <t xml:space="preserve">Pavlína Koutecká, Premysl Sucha, Jan Hůla, Broos Maenhout </t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang H. Nguyen, Marcelo Menegali, Junehyuk Jung, Junsu Kim, Vikas Verma, Quoc V. Le, Thang Luong </t>
+          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olšák, Xiaomeng Yang, Hoang H. Nguyen, Marcelo Menegali, Junehyuk Jung, Junsu Kim, Vikas Verma, Quoc V. Le, Thang Luong </t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3991,7 +3991,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelle Piepenbrock, Josef Urban, Konstantin Korovin, Miroslav Olsák, Tom Heskes, Mikolás Janota </t>
+          <t xml:space="preserve">Jelle Piepenbrock, Josef Urban, Konstantin Korovin, Miroslav Olšák, Tom Heskes, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4021,7 +4021,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Mojzísek, Jan Hula, Jirí Janecek, David Herel, Mikolás Janota </t>
+          <t xml:space="preserve">David Mojzísek, Jan Hůla, Jiří Janecek, David Herel, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4081,7 +4081,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Osama Mazhar, Robert Babuska, Jens Kober </t>
+          <t xml:space="preserve">Osama Mazhar, Robert Babuška, Jens Kober </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4111,7 +4111,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Vanc, Giovanni Franzese, Jan Kristof Behrens, Cosimo Della Santina, Karla Stépánová, Jens Kober, Robert Babuska </t>
+          <t xml:space="preserve">Petr Vanc, Giovanni Franzese, Jan Kristof Behrens, Cosimo Della Santina, Karla Stépánová, Jens Kober, Robert Babuška </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4141,7 +4141,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bas van der Heijden, Jelle Luijkx, Laura Ferranti, Jens Kober, Robert Babuska </t>
+          <t xml:space="preserve">Bas van der Heijden, Jelle Luijkx, Laura Ferranti, Jens Kober, Robert Babuška </t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4171,7 +4171,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Fajcik, Martin Docekal, Jan Dolezal, Karel Ondrej, Karel Benes, Jan Kapsa, Pavel Smrz, Alexander Polok, Michal Hradis, Zuzana Neverilová, Ales Horák, Radoslav Sabol, Michal Stefánik, Adam Jirkovsky, David Adamczyk, Petr Hyner, Jan Hula, Hynek Kydlícek </t>
+          <t xml:space="preserve">Martin Fajcik, Martin Docekal, Jan Dolezal, Karel Ondrej, Karel Benes, Jan Kapsa, Pavel Smrz, Alexander Polok, Michal Hradis, Zuzana Neverilová, Ales Horák, Radoslav Sabol, Michal Stefánik, Adam Jirkovsky, David Adamczyk, Petr Hyner, Jan Hůla, Hynek Kydlícek </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bas van der Heijden, Jens Kober, Robert Babuska, Laura Ferranti </t>
+          <t xml:space="preserve">Bas van der Heijden, Jens Kober, Robert Babuška, Laura Ferranti </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Benders, Johannes Köhler, Thijs Niesten, Robert Babuska, Javier Alonso-Mora, Laura Ferranti </t>
+          <t xml:space="preserve">Dennis Benders, Johannes Köhler, Thijs Niesten, Robert Babuška, Javier Alonso-Mora, Laura Ferranti </t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4291,7 +4291,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Choiwah Chow, João Araújo, Michael Codish, Petr Vojtechovský </t>
+          <t xml:space="preserve">Mikoláš Janota, Choiwah Chow, João Araújo, Michael Codish, Petr Vojtechovský </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, David M. Cerna, Thibault Gauthier, Jan Jakubuv, Cezary Kaliszyk, Martin Suda, Josef Urban </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, David M. Cerna, Thibault Gauthier, Jan Jakubův, Cezary Kaliszyk, Martin Suda, Josef Urban </t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Mojzísek, Mikolás Janota </t>
+          <t xml:space="preserve">Jan Hůla, David Mojzísek, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Choiwah Chow, Mikolás Janota, João Araújo </t>
+          <t xml:space="preserve">Choiwah Chow, Mikoláš Janota, João Araújo </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Mikolás Janota, Jelle Piepenbrock, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Mikoláš Janota, Jelle Piepenbrock, Josef Urban </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco M. Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco M. Manquinho </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4621,7 +4621,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simon Frieder, Mirek Olsák, Julius Berner, Thomas Lukasiewicz </t>
+          <t xml:space="preserve">Simon Frieder, Mirek Olšák, Julius Berner, Thomas Lukasiewicz </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4651,7 +4651,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Herel, Tomás Mikolov </t>
+          <t xml:space="preserve">David Herel, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4711,7 +4711,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Mirek Olsák, Jason Rute, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Mirek Olšák, Jason Rute, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikail Khona, Maya Okawa, Jan Hula, Rahul Ramesh, Kento Nishi, Robert P. Dick, Ekdeep Singh Lubana, Hidenori Tanaka </t>
+          <t xml:space="preserve">Mikail Khona, Maya Okawa, Jan Hůla, Rahul Ramesh, Kento Nishi, Robert P. Dick, Ekdeep Singh Lubana, Hidenori Tanaka </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Adamczyk, Jan Hula </t>
+          <t xml:space="preserve">David Adamczyk, Jan Hůla </t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4801,7 +4801,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Mojzísek, Jan Hula </t>
+          <t xml:space="preserve">David Mojzísek, Jan Hůla </t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4831,7 +4831,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luuk van den Bent, Tomás Coleman, Robert Babuska </t>
+          <t xml:space="preserve">Luuk van den Bent, Tomás Coleman, Robert Babuška </t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4861,7 +4861,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hyner, Petr Marek, David Adamczyk, Jan Hula, Jan Sedivý </t>
+          <t xml:space="preserve">Petr Hyner, Petr Marek, David Adamczyk, Jan Hůla, Jan Sedivý </t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Balyo, Martin Suda, Lukás Chrpa, Dominik Safránek, Stephan Gocht, Filip Dvorák, Roman Barták, G. Michael Youngblood </t>
+          <t xml:space="preserve">Tomáš Balyo, Martin Suda, Lukás Chrpa, Dominik Safránek, Stephan Gocht, Filip Dvorák, Roman Barták, G. Michael Youngblood </t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kristina Aleksandrova, Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Kristina Aleksandrova, Jan Jakubův, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5161,7 +5161,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelle Piepenbrock, Mikolas Janota, Josef Urban, Jan Jakubuv </t>
+          <t xml:space="preserve">Jelle Piepenbrock, Mikoláš Janota, Josef Urban, Jan Jakubův </t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Coleman, Robert Babuska, Jens Kober, Cosimo Della Santina </t>
+          <t xml:space="preserve">Tomás Coleman, Robert Babuška, Jens Kober, Cosimo Della Santina </t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5251,7 +5251,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Mikolás Janota, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Mikoláš Janota, Josef Urban </t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Tobias Fischer, Jonáš Kulhánek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5341,7 +5341,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5431,7 +5431,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Mikolas Janota, Mirek Olsák </t>
+          <t xml:space="preserve">Chad E. Brown, Mikoláš Janota, Mirek Olšák </t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5461,7 +5461,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5521,7 +5521,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Peitl, Markus Kirchweger, Mikolás Janota, Stefan Szeider </t>
+          <t xml:space="preserve">Tomáš Peitl, Markus Kirchweger, Mikoláš Janota, Stefan Szeider </t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Kristina Batistic, Jan Zahálka, Robert Babuska </t>
+          <t xml:space="preserve">Erik Derner, Kristina Batistic, Jan Zahálka, Robert Babuška </t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Jonas Kulhanek, Jirí Kubalík, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Martin Vastl, Jonáš Kulhánek, Jiří Kubalík, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olšák, Herman Geuvers </t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5731,7 +5731,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Rute, Miroslav Olsák, Lasse Blaauwbroek, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
+          <t xml:space="preserve">Jason Rute, Miroslav Olšák, Lasse Blaauwbroek, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5851,7 +5851,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shervin Minaee, Tomás Mikolov, Narjes Nikzad, Meysam Chenaghlu, Richard Socher, Xavier Amatriain, Jianfeng Gao </t>
+          <t xml:space="preserve">Shervin Minaee, Tomáš Mikolov, Narjes Nikzad, Meysam Chenaghlu, Richard Socher, Xavier Amatriain, Jianfeng Gao </t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5881,7 +5881,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikail Khona, Maya Okawa, Jan Hula, Rahul Ramesh, Kento Nishi, Robert P. Dick, Ekdeep Singh Lubana, Hidenori Tanaka </t>
+          <t xml:space="preserve">Mikail Khona, Maya Okawa, Jan Hůla, Rahul Ramesh, Kento Nishi, Robert P. Dick, Ekdeep Singh Lubana, Hidenori Tanaka </t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5911,7 +5911,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Balyo, Martin Suda, Lukás Chrpa, Dominik Safránek, Filip Dvorák, Roman Barták, G. Michael Youngblood </t>
+          <t xml:space="preserve">Tomáš Balyo, Martin Suda, Lukás Chrpa, Dominik Safránek, Filip Dvorák, Roman Barták, G. Michael Youngblood </t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5941,7 +5941,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, David M. Cerna, Thibault Gauthier, Jan Jakubuv, Cezary Kaliszyk, Martin Suda, Josef Urban </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, David M. Cerna, Thibault Gauthier, Jan Jakubův, Cezary Kaliszyk, Martin Suda, Josef Urban </t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Herel, Tomás Mikolov </t>
+          <t xml:space="preserve">David Herel, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6061,7 +6061,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Mikolás Janota, Mirek Olsák </t>
+          <t xml:space="preserve">Chad E. Brown, Mikoláš Janota, Mirek Olšák </t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6091,7 +6091,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Herel, Tomás Mikolov </t>
+          <t xml:space="preserve">David Herel, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Tobias Fischer, Jonáš Kulhánek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6181,7 +6181,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Benders, Johannes Köhler, Thijs Niesten, Robert Babuska, Javier Alonso-Mora, Laura Ferranti </t>
+          <t xml:space="preserve">Dennis Benders, Johannes Köhler, Thijs Niesten, Robert Babuška, Javier Alonso-Mora, Laura Ferranti </t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6241,7 +6241,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6271,7 +6271,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Mikolás Janota, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Mikoláš Janota, Josef Urban </t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6301,7 +6301,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bas van der Heijden, Jelle Luijkx, Laura Ferranti, Jens Kober, Robert Babuska </t>
+          <t xml:space="preserve">Bas van der Heijden, Jelle Luijkx, Laura Ferranti, Jens Kober, Robert Babuška </t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6361,7 +6361,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6391,7 +6391,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6421,7 +6421,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonáš Kulhánek </t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6451,7 +6451,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Mikolás Janota, Jelle Piepenbrock, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Mikoláš Janota, Jelle Piepenbrock, Josef Urban </t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6481,7 +6481,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Mojzísek, Mikolás Janota </t>
+          <t xml:space="preserve">Jan Hůla, David Mojzísek, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6511,7 +6511,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodrigo Pérez-Dattari, Zhaoting Li, Robert Babuska, Jens Kober, Cosimo Della Santina </t>
+          <t xml:space="preserve">Rodrigo Pérez-Dattari, Zhaoting Li, Robert Babuška, Jens Kober, Cosimo Della Santina </t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6541,7 +6541,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6571,7 +6571,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Herel, Vojtech Bartek, Tomás Mikolov </t>
+          <t xml:space="preserve">David Herel, Vojtech Bartek, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6661,7 +6661,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liao Zhang, Fabian Mitterwallner, Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Liao Zhang, Fabian Mitterwallner, Jan Jakubův, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6721,7 +6721,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Fajcik, Martin Docekal, Jan Dolezal, Karel Ondrej, Karel Benes, Jan Kapsa, Pavel Smrz, Alexander Polok, Michal Hradis, Zuzana Neverilová, Ales Horák, Radoslav Sabol, Michal Stefánik, Adam Jirkovsky, David Adamczyk, Petr Hyner, Jan Hula, Hynek Kydlícek </t>
+          <t xml:space="preserve">Martin Fajcik, Martin Docekal, Jan Dolezal, Karel Ondrej, Karel Benes, Jan Kapsa, Pavel Smrz, Alexander Polok, Michal Hradis, Zuzana Neverilová, Ales Horák, Radoslav Sabol, Michal Stefánik, Adam Jirkovsky, David Adamczyk, Petr Hyner, Jan Hůla, Hynek Kydlícek </t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olšák, Herman Geuvers </t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6901,7 +6901,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bas van der Heijden, Laura Ferranti, Jens Kober, Robert Babuska </t>
+          <t xml:space="preserve">Bas van der Heijden, Laura Ferranti, Jens Kober, Robert Babuška </t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Araújo, Choiwah Chow, Mikolás Janota </t>
+          <t xml:space="preserve">João Araújo, Choiwah Chow, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7021,7 +7021,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Herel, Hugo Cisneros, Tomás Mikolov </t>
+          <t xml:space="preserve">David Herel, Hugo Cisneros, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7051,7 +7051,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Jelle Piepenbrock, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Jelle Piepenbrock, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7081,7 +7081,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nikolai Antonov, Premysl Sucha, Mikolás Janota </t>
+          <t xml:space="preserve">Nikolai Antonov, Premysl Sucha, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7111,7 +7111,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolas Janota, Nina Narodytska </t>
+          <t xml:space="preserve">Mikoláš Janota, Nina Narodytska </t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7231,7 +7231,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Adamczyk, Mikolás Janota </t>
+          <t xml:space="preserve">Jan Hůla, David Adamczyk, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7261,7 +7261,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7291,7 +7291,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hyner, Jan Hula, Mikolás Janota </t>
+          <t xml:space="preserve">Petr Hyner, Jan Hůla, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7351,7 +7351,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Karel Chvalovský, Zarathustra Amadeus Goertzel, Cezary Kaliszyk, Mirek Olsák, Bartosz Piotrowski, Stephan Schulz, Martin Suda, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Karel Chvalovský, Zarathustra Amadeus Goertzel, Cezary Kaliszyk, Mirek Olšák, Bartosz Piotrowski, Stephan Schulz, Martin Suda, Josef Urban </t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7441,7 +7441,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Chad E. Brown, Mikolas Janota, Josef Urban </t>
+          <t xml:space="preserve">Thibault Gauthier, Chad E. Brown, Mikoláš Janota, Josef Urban </t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7471,7 +7471,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julian Parsert, Chad E. Brown, Mikolas Janota, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Julian Parsert, Chad E. Brown, Mikoláš Janota, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7501,7 +7501,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Jan Jakubův, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7531,7 +7531,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Mikolás Janota, Bartosz Piotrowski, Jelle Piepenbrock, Andrew Reynolds </t>
+          <t xml:space="preserve">Jan Jakubův, Mikoláš Janota, Bartosz Piotrowski, Jelle Piepenbrock, Andrew Reynolds </t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7561,7 +7561,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Bartosz Piotrowski, Karel Chvalovský </t>
+          <t xml:space="preserve">Mikoláš Janota, Bartosz Piotrowski, Karel Chvalovský </t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7681,7 +7681,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7711,7 +7711,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Miroslav Olsák, Josef Urban </t>
+          <t xml:space="preserve">Thibault Gauthier, Miroslav Olšák, Josef Urban </t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7741,7 +7741,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7801,7 +7801,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Karel Chvalovský, Zarathustra Amadeus Goertzel, Cezary Kaliszyk, Mirek Olsák, Bartosz Piotrowski, Stephan Schulz, Martin Suda, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Karel Chvalovský, Zarathustra Amadeus Goertzel, Cezary Kaliszyk, Mirek Olšák, Bartosz Piotrowski, Stephan Schulz, Martin Suda, Josef Urban </t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7861,7 +7861,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Chad E. Brown, Mikolas Janota, Josef Urban </t>
+          <t xml:space="preserve">Thibault Gauthier, Chad E. Brown, Mikoláš Janota, Josef Urban </t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7891,7 +7891,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7981,7 +7981,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Jelle Piepenbrock, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Jelle Piepenbrock, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -8041,7 +8041,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luuk van den Bent, Tomás Coleman, Robert Babuska </t>
+          <t xml:space="preserve">Luuk van den Bent, Tomás Coleman, Robert Babuška </t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Kristina Batistic, Jan Zahálka, Robert Babuska </t>
+          <t xml:space="preserve">Erik Derner, Kristina Batistic, Jan Zahálka, Robert Babuška </t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8191,7 +8191,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Herel, Tomás Mikolov </t>
+          <t xml:space="preserve">David Herel, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8251,7 +8251,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mohammad Rohaninejad, Mikolás Janota, Zdenek Hanzálek </t>
+          <t xml:space="preserve">Mohammad Rohaninejad, Mikoláš Janota, Zdenek Hanzálek </t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8341,7 +8341,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Miroslav Olsák, Josef Urban </t>
+          <t xml:space="preserve">Thibault Gauthier, Miroslav Olšák, Josef Urban </t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8371,7 +8371,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, António Morgado, Petr Vojtechovský </t>
+          <t xml:space="preserve">Mikoláš Janota, António Morgado, Petr Vojtechovský </t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8401,7 +8401,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Sedlár, Karla Stépánová, Radoslav Skoviera, Jan Kristof Behrens, Matús Tuna, Gabriela Sejnova, Josef Sivic, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Sedlár, Karla Stépánová, Radoslav Skoviera, Jan Kristof Behrens, Matús Tuna, Gabriela Sejnova, Josef Sivic, Robert Babuška </t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8491,7 +8491,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelle Piepenbrock, Tom Heskes, Mikolás Janota, Josef Urban </t>
+          <t xml:space="preserve">Jelle Piepenbrock, Tom Heskes, Mikoláš Janota, Josef Urban </t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8581,7 +8581,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hugo Cisneros, Tomás Mikolov, Josef Sivic </t>
+          <t xml:space="preserve">Hugo Cisneros, Tomáš Mikolov, Josef Sivic </t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8611,7 +8611,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Erik Derner, Torsten Sattler, Robert Babuska </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Erik Derner, Torsten Sattler, Robert Babuška </t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8641,7 +8641,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max Lodel, Bruno Brito, Álvaro Serra-Gómez, Laura Ferranti, Robert Babuska, Javier Alonso-Mora </t>
+          <t xml:space="preserve">Max Lodel, Bruno Brito, Álvaro Serra-Gómez, Laura Ferranti, Robert Babuška, Javier Alonso-Mora </t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8671,7 +8671,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Mojzísek, David Adamczyk </t>
+          <t xml:space="preserve">Jan Hůla, David Mojzísek, David Adamczyk </t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8701,7 +8701,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nikolaos Passalis, S. Pedrazzi, Robert Babuska, Wolfram Burgard, D. Dias, F. Ferro, Moncef Gabbouj, Ole Green, Alexandros Iosifidis, Erdal Kayacan, Jens Kober, O. Michel, Nikos Nikolaidis, Paraskevi Nousi, Roel Pieters, Maria Tzelepi, Abhinav Valada, Anastasios Tefas </t>
+          <t xml:space="preserve">Nikolaos Passalis, S. Pedrazzi, Robert Babuška, Wolfram Burgard, D. Dias, F. Ferro, Moncef Gabbouj, Ole Green, Alexandros Iosifidis, Erdal Kayacan, Jens Kober, O. Michel, Nikos Nikolaidis, Paraskevi Nousi, Roel Pieters, Maria Tzelepi, Abhinav Valada, Anastasios Tefas </t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8731,7 +8731,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xinying Chen, Jan Hula, Antonín Dvorák </t>
+          <t xml:space="preserve">Xinying Chen, Jan Hůla, Antonín Dvorák </t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8761,7 +8761,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Mojzísek, Jan Hula </t>
+          <t xml:space="preserve">David Mojzísek, Jan Hůla </t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8791,7 +8791,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubuv, Cezary Kaliszyk, Miroslav Olsák, Jelle Piepenbrock, Josef Urban </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubův, Cezary Kaliszyk, Miroslav Olšák, Jelle Piepenbrock, Josef Urban </t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8821,7 +8821,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, Jan Jakubuv, Mikolás Janota, Lukás Kubej </t>
+          <t xml:space="preserve">Jan Hůla, Jan Jakubův, Mikoláš Janota, Lukás Kubej </t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8941,7 +8941,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filipe Marques, António Morgado, José Fragoso Santos, Mikolás Janota </t>
+          <t xml:space="preserve">Filipe Marques, António Morgado, José Fragoso Santos, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8971,7 +8971,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miguel Cabral, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Miguel Cabral, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -9031,7 +9031,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Jelle Piepenbrock, Bartosz Piotrowski </t>
+          <t xml:space="preserve">Mikoláš Janota, Jelle Piepenbrock, Bartosz Piotrowski </t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -9061,7 +9061,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9091,7 +9091,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Mikolás Janota, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Chad E. Brown, Mikoláš Janota, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9151,7 +9151,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padmaja Kulkarni, Jens Kober, Robert Babuska, Cosimo Della Santina </t>
+          <t xml:space="preserve">Padmaja Kulkarni, Jens Kober, Robert Babuška, Cosimo Della Santina </t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9181,7 +9181,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Tomás Mikolov </t>
+          <t xml:space="preserve">Barbora Hudcová, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9211,7 +9211,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán Kruszewski, Tomás Mikolov </t>
+          <t xml:space="preserve">Germán Kruszewski, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9241,7 +9241,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Araújo, Choiwah Chow, Mikolás Janota </t>
+          <t xml:space="preserve">João Araújo, Choiwah Chow, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9271,7 +9271,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Araújo, Choiwah Chow, Mikolás Janota </t>
+          <t xml:space="preserve">João Araújo, Choiwah Chow, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9361,7 +9361,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nikolaos Passalis, S. Pedrazzi, Robert Babuska, Wolfram Burgard, D. Dias, F. Ferro, Moncef Gabbouj, Ole Green, Alexandros Iosifidis, Erdal Kayacan, Jens Kober, O. Michel, Nikolaos Nikolaidis, Paraskevi Nousi, Roel Pieters, Maria Tzelepi, Abhinav Valada, Anastasios Tefas </t>
+          <t xml:space="preserve">Nikolaos Passalis, S. Pedrazzi, Robert Babuška, Wolfram Burgard, D. Dias, F. Ferro, Moncef Gabbouj, Ole Green, Alexandros Iosifidis, Erdal Kayacan, Jens Kober, O. Michel, Nikolaos Nikolaidis, Paraskevi Nousi, Roel Pieters, Maria Tzelepi, Abhinav Valada, Anastasios Tefas </t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -9391,7 +9391,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max Lodel, Bruno Brito, Álvaro Serra-Gómez, Laura Ferranti, Robert Babuska, Javier Alonso-Mora </t>
+          <t xml:space="preserve">Max Lodel, Bruno Brito, Álvaro Serra-Gómez, Laura Ferranti, Robert Babuška, Javier Alonso-Mora </t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -9421,7 +9421,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Erik Derner, Torsten Sattler, Robert Babuska </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Erik Derner, Torsten Sattler, Robert Babuška </t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -9481,7 +9481,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubuv, Cezary Kaliszyk, Miroslav Olsák, Jelle Piepenbrock, Josef Urban </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubův, Cezary Kaliszyk, Miroslav Olšák, Jelle Piepenbrock, Josef Urban </t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9541,7 +9541,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Jonas Kulhanek, Jirí Kubalík, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Martin Vastl, Jonáš Kulhánek, Jiří Kubalík, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9571,7 +9571,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9601,7 +9601,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedro Orvalho, Mikolás Janota, Vasco Manquinho </t>
+          <t xml:space="preserve">Pedro Orvalho, Mikoláš Janota, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -9631,7 +9631,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Herel, Dominika Zogatova, Matej Kripner, Tomás Mikolov </t>
+          <t xml:space="preserve">David Herel, Dominika Zogatova, Matej Kripner, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -9661,7 +9661,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filipe Marques, António Morgado, José Fragoso Santos, Mikolás Janota </t>
+          <t xml:space="preserve">Filipe Marques, António Morgado, José Fragoso Santos, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -9721,7 +9721,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Sedlár, Karla Stépánová, Matús Tuna, Radoslav Skoviera, Jan Kristof Behrens, Gabriela Sejnova, Josef Sivic, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Sedlár, Karla Stépánová, Matús Tuna, Radoslav Skoviera, Jan Kristof Behrens, Gabriela Sejnova, Josef Sivic, Robert Babuška </t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9751,7 +9751,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hugo Cisneros, Josef Sivic, Tomás Mikolov </t>
+          <t xml:space="preserve">Hugo Cisneros, Josef Sivic, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -9781,7 +9781,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelle Piepenbrock, Josef Urban, Konstantin Korovin, Miroslav Olsák, Tom Heskes, Mikolas Janota </t>
+          <t xml:space="preserve">Jelle Piepenbrock, Josef Urban, Konstantin Korovin, Miroslav Olšák, Tom Heskes, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -9841,7 +9841,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Herel, Hugo Cisneros, Tomás Mikolov </t>
+          <t xml:space="preserve">David Herel, Hugo Cisneros, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -9901,7 +9901,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hula, Marek Vajgl, Pavel Vlasánek, Tomas Nejezchleba </t>
+          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hůla, Marek Vajgl, Pavel Vlasánek, Tomáš Nejezchleba </t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9931,7 +9931,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hurtík, Stefania Tomasiello, Jan Hula, David Hynar </t>
+          <t xml:space="preserve">Petr Hurtík, Stefania Tomasiello, Jan Hůla, David Hynar </t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9961,7 +9961,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Preucil, Robert Babuska </t>
+          <t xml:space="preserve">Libor Preucil, Robert Babuška </t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -10111,7 +10111,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Araújo, Choiwah Chow, Mikolás Janota </t>
+          <t xml:space="preserve">João Araújo, Choiwah Chow, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10141,7 +10141,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, António Morgado, José Fragoso Santos, Vasco Manquinho </t>
+          <t xml:space="preserve">Mikoláš Janota, António Morgado, José Fragoso Santos, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -10171,7 +10171,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Haniel Barbosa, Pascal Fontaine, Andrew Reynolds </t>
+          <t xml:space="preserve">Mikoláš Janota, Haniel Barbosa, Pascal Fontaine, Andrew Reynolds </t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -10201,7 +10201,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Karel Chvalovský, Jan Jakubuv, Miroslav Olsák, Josef Urban </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Karel Chvalovský, Jan Jakubův, Miroslav Olšák, Josef Urban </t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -10291,7 +10291,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Mojzísek, Mikolás Janota </t>
+          <t xml:space="preserve">Jan Hůla, David Mojzísek, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10351,7 +10351,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov </t>
+          <t xml:space="preserve">Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -10381,7 +10381,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Jirí Kubalík, Robert Babuska </t>
+          <t xml:space="preserve">Erik Derner, Jiří Kubalík, Robert Babuška </t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -10411,7 +10411,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bas van der Heijden, Laura Ferranti, Jens Kober, Robert Babuska </t>
+          <t xml:space="preserve">Bas van der Heijden, Laura Ferranti, Jens Kober, Robert Babuška </t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -10441,7 +10441,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacob E. Kooi, Robert Babuska </t>
+          <t xml:space="preserve">Jacob E. Kooi, Robert Babuška </t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -10471,7 +10471,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Tomás Mikolov </t>
+          <t xml:space="preserve">Barbora Hudcová, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -10501,7 +10501,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Adamczyk, David Mojzísek, Vojtech Molek </t>
+          <t xml:space="preserve">Jan Hůla, David Adamczyk, David Mojzísek, Vojtech Molek </t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -10591,7 +10591,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaroslav Macke, Jirí Sedlár, Miroslav Olsák, Josef Urban, Josef Sivic </t>
+          <t xml:space="preserve">Jaroslav Macke, Jiří Sedlár, Miroslav Olšák, Josef Urban, Josef Sivic </t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -10771,7 +10771,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Bagatella, Miroslav Olsák, Michal Rolínek, Georg Martius </t>
+          <t xml:space="preserve">Marco Bagatella, Miroslav Olšák, Michal Rolínek, Georg Martius </t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -10831,7 +10831,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Mikolás Janota </t>
+          <t xml:space="preserve">Chad E. Brown, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -10861,7 +10861,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Mikolás Janota, Andrew Reynolds </t>
+          <t xml:space="preserve">Jan Jakubův, Mikoláš Janota, Andrew Reynolds </t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -10921,7 +10921,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karel Chvalovský, Jan Jakubuv, Miroslav Olsák, Josef Urban </t>
+          <t xml:space="preserve">Karel Chvalovský, Jan Jakubův, Miroslav Olšák, Josef Urban </t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -10981,7 +10981,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsolt Zombori, Josef Urban, Miroslav Olsák </t>
+          <t xml:space="preserve">Zsolt Zombori, Josef Urban, Miroslav Olšák </t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -11011,7 +11011,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Jirí Kubalík, Robert Babuska </t>
+          <t xml:space="preserve">Erik Derner, Jiří Kubalík, Robert Babuška </t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -11041,7 +11041,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Erik Derner, Jan Zegklitz, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Erik Derner, Jan Zegklitz, Robert Babuška </t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -11101,7 +11101,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Brablc, Jan Zegklitz, Robert Grepl, Robert Babuska </t>
+          <t xml:space="preserve">Martin Brablc, Jan Zegklitz, Robert Grepl, Robert Babuška </t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -11191,7 +11191,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Vojtech Hudecek, Tomáš Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -11221,7 +11221,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelle Piepenbrock, Tom Heskes, Mikolás Janota, Josef Urban </t>
+          <t xml:space="preserve">Jelle Piepenbrock, Tom Heskes, Mikoláš Janota, Josef Urban </t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11251,7 +11251,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Osama Mazhar, Jens Kober, Robert Babuska </t>
+          <t xml:space="preserve">Osama Mazhar, Jens Kober, Robert Babuška </t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11311,7 +11311,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taeke de Haan, Padmaja Kulkarni, Robert Babuska </t>
+          <t xml:space="preserve">Taeke de Haan, Padmaja Kulkarni, Robert Babuška </t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán Kruszewski, Tomás Mikolov </t>
+          <t xml:space="preserve">Germán Kruszewski, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -11371,7 +11371,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacob E. Kooi, Robert Babuska </t>
+          <t xml:space="preserve">Jacob E. Kooi, Robert Babuška </t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -11401,7 +11401,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hugo Cisneros, Josef Sivic, Tomás Mikolov </t>
+          <t xml:space="preserve">Hugo Cisneros, Josef Sivic, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -11461,7 +11461,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Haniel Barbosa, Pascal Fontaine, Andrew Reynolds </t>
+          <t xml:space="preserve">Mikoláš Janota, Haniel Barbosa, Pascal Fontaine, Andrew Reynolds </t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -11491,7 +11491,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsolt Zombori, Josef Urban, Miroslav Olsák </t>
+          <t xml:space="preserve">Zsolt Zombori, Josef Urban, Miroslav Olšák </t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -11521,7 +11521,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaroslav Macke, Jirí Sedlár, Miroslav Olsák, Josef Urban, Josef Sivic </t>
+          <t xml:space="preserve">Jaroslav Macke, Jiří Sedlár, Miroslav Olšák, Josef Urban, Josef Sivic </t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -11551,7 +11551,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Karel Chvalovský, Jan Jakubuv, Miroslav Olsák, Josef Urban </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Karel Chvalovský, Jan Jakubův, Miroslav Olšák, Josef Urban </t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -11581,7 +11581,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karel Chvalovský, Jan Jakubuv, Miroslav Olsák, Josef Urban </t>
+          <t xml:space="preserve">Karel Chvalovský, Jan Jakubův, Miroslav Olšák, Josef Urban </t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -11611,7 +11611,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Tomás Mikolov </t>
+          <t xml:space="preserve">Barbora Hudcová, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -11641,7 +11641,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Tomás Mikolov </t>
+          <t xml:space="preserve">Barbora Hudcová, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -11701,7 +11701,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Bagatella, Mirek Olsák, Michal Rolínek, Georg Martius </t>
+          <t xml:space="preserve">Marco Bagatella, Mirek Olšák, Michal Rolínek, Georg Martius </t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -11761,7 +11761,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -11851,7 +11851,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olšák, Trung Van Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -11881,7 +11881,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Miroslav Olšák </t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -11911,7 +11911,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -11941,7 +11941,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Osama Mazhar, Robert Babuska, Jens Kober </t>
+          <t xml:space="preserve">Osama Mazhar, Robert Babuška, Jens Kober </t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -11971,7 +11971,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Clara Gómez, Alejandra C. Hernández, Ramón Barber, Robert Babuska </t>
+          <t xml:space="preserve">Erik Derner, Clara Gómez, Alejandra C. Hernández, Ramón Barber, Robert Babuška </t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -12061,7 +12061,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Mikolás Janota, Florian Lonsing, Martina Seidl </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Mikoláš Janota, Florian Lonsing, Martina Seidl </t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -12241,7 +12241,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Karel Chvalovský, Miroslav Olsák, Bartosz Piotrowski, Martin Suda, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Karel Chvalovský, Miroslav Olšák, Bartosz Piotrowski, Martin Suda, Josef Urban </t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -12331,7 +12331,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula </t>
+          <t xml:space="preserve">Jan Hůla </t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -12361,7 +12361,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Mojzísek, David Adamczyk, Radek Cech </t>
+          <t xml:space="preserve">Jan Hůla, David Mojzísek, David Adamczyk, Radek Cech </t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -12391,7 +12391,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák, Cezary Kaliszyk, Josef Urban </t>
+          <t xml:space="preserve">Miroslav Olšák, Cezary Kaliszyk, Josef Urban </t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -12481,7 +12481,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -12511,7 +12511,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Miroslav Olšák </t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -12541,7 +12541,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Kristof Behrens, Karla Stépánová, Robert Babuska </t>
+          <t xml:space="preserve">Jan Kristof Behrens, Karla Stépánová, Robert Babuška </t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -12571,7 +12571,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alejandra C. Hernández, Erik Derner, Clara Gómez, Ramón Barber, Robert Babuska </t>
+          <t xml:space="preserve">Alejandra C. Hernández, Erik Derner, Clara Gómez, Ramón Barber, Robert Babuška </t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -12601,7 +12601,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hugo Cisneros, Josef Sivic, Tomás Mikolov </t>
+          <t xml:space="preserve">Hugo Cisneros, Josef Sivic, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -12631,7 +12631,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Tomás Mikolov </t>
+          <t xml:space="preserve">Barbora Hudcová, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -12661,7 +12661,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán Kruszewski, Tomás Mikolov </t>
+          <t xml:space="preserve">Germán Kruszewski, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -12691,7 +12691,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padmaja Kulkarni, Jens Kober, Robert Babuska </t>
+          <t xml:space="preserve">Padmaja Kulkarni, Jens Kober, Robert Babuška </t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -12721,7 +12721,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Adamczyk, Jan Hula </t>
+          <t xml:space="preserve">David Adamczyk, Jan Hůla </t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -12991,7 +12991,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josef Urban, Jan Jakubuv </t>
+          <t xml:space="preserve">Josef Urban, Jan Jakubův </t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -13141,7 +13141,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, António Morgado </t>
+          <t xml:space="preserve">Mikoláš Janota, António Morgado </t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -13171,7 +13171,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuda van Diggelen, Robert Babuska, A. E. Eiben </t>
+          <t xml:space="preserve">Fuda van Diggelen, Robert Babuška, A. E. Eiben </t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -13201,7 +13201,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Jirí Kubalík, Nicola Ancona, Robert Babuska </t>
+          <t xml:space="preserve">Erik Derner, Jiří Kubalík, Nicola Ancona, Robert Babuška </t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -13291,7 +13291,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Karel Chvalovský, Miroslav Olsák, Bartosz Piotrowski, Martin Suda, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Karel Chvalovský, Miroslav Olšák, Bartosz Piotrowski, Martin Suda, Josef Urban </t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -13321,7 +13321,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán Kruszewski, Tomás Mikolov </t>
+          <t xml:space="preserve">Germán Kruszewski, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -13381,7 +13381,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán Kruszewski, Ionut-Teodor Sorodoc, Tomás Mikolov </t>
+          <t xml:space="preserve">Germán Kruszewski, Ionut-Teodor Sorodoc, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -13531,7 +13531,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -13591,7 +13591,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Miroslav Olšák </t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -13651,7 +13651,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hula, Marek Vajgl, Pavel Vlasánek, Tomas Nejezchleba </t>
+          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hůla, Marek Vajgl, Pavel Vlasánek, Tomáš Nejezchleba </t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -13681,7 +13681,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josef Urban, Jan Jakubuv </t>
+          <t xml:space="preserve">Josef Urban, Jan Jakubův </t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -13711,7 +13711,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
+          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olšák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -13741,7 +13741,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
+          <t xml:space="preserve">Miroslav Kulich, Jiří Kubalík, Libor Preucil </t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -13801,7 +13801,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Tomás Mikolov </t>
+          <t xml:space="preserve">Barbora Hudcová, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -13951,7 +13951,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -13981,7 +13981,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bas van der Heijden, Laura Ferranti, Jens Kober, Robert Babuska </t>
+          <t xml:space="preserve">Bas van der Heijden, Laura Ferranti, Jens Kober, Robert Babuška </t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -14071,7 +14071,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Miroslav Olšák </t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -14131,7 +14131,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dagmar Monett, Colin W. P. Lewis, Kristinn R. Thórisson, Joscha Bach, Gianluca Baldassarre, Giovanni Granato, Istvan S. N. Berkeley, François Chollet, Matthew Crosby, Henry Shevlin, John F. Sowa, John E. Laird, Shane Legg, Peter Lindes, Tomás Mikolov, William J. Rapaport, Raúl Rojas, Marek Rosa, Peter Stone, Richard S. Sutton, Roman V. Yampolskiy, Pei Wang, Roger C. Schank, Aaron Sloman, Alan F. T. Winfield </t>
+          <t xml:space="preserve">Dagmar Monett, Colin W. P. Lewis, Kristinn R. Thórisson, Joscha Bach, Gianluca Baldassarre, Giovanni Granato, Istvan S. N. Berkeley, François Chollet, Matthew Crosby, Henry Shevlin, John F. Sowa, John E. Laird, Shane Legg, Peter Lindes, Tomáš Mikolov, William J. Rapaport, Raúl Rojas, Marek Rosa, Peter Stone, Richard S. Sutton, Roman V. Yampolskiy, Pei Wang, Roger C. Schank, Aaron Sloman, Alan F. T. Winfield </t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -14161,7 +14161,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Jan Jakubův, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -14221,7 +14221,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber, Robert Babuska </t>
+          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber, Robert Babuška </t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -14251,7 +14251,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hula </t>
+          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hůla </t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -14281,7 +14281,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Wang, Jan Hula, Patrick Xia, Raghavendra Pappagari, R. Thomas McCoy, Roma Patel, Najoung Kim, Ian Tenney, Yinghui Huang, Katherin Yu, Shuning Jin, Berlin Chen, Benjamin Van Durme, Edouard Grave, Ellie Pavlick, Samuel R. Bowman </t>
+          <t xml:space="preserve">Alex Wang, Jan Hůla, Patrick Xia, Raghavendra Pappagari, R. Thomas McCoy, Roma Patel, Najoung Kim, Ian Tenney, Yinghui Huang, Katherin Yu, Shuning Jin, Berlin Chen, Benjamin Van Durme, Edouard Grave, Ellie Pavlick, Samuel R. Bowman </t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -14371,7 +14371,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karel Chvalovský, Jan Jakubuv, Martin Suda, Josef Urban </t>
+          <t xml:space="preserve">Karel Chvalovský, Jan Jakubův, Martin Suda, Josef Urban </t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -14401,7 +14401,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Clara Gómez, Alejandra C. Hernández, Ramón Barber, Robert Babuska </t>
+          <t xml:space="preserve">Erik Derner, Clara Gómez, Alejandra C. Hernández, Ramón Barber, Robert Babuška </t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -14491,7 +14491,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Erik Derner, Tim de Bruin, Robert Babuska </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Erik Derner, Tim de Bruin, Robert Babuška </t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -14521,7 +14521,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -14551,7 +14551,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simon Cooksey, Sarah Harris, Mark Batty, Radu Grigore, Mikolás Janota </t>
+          <t xml:space="preserve">Simon Cooksey, Sarah Harris, Mark Batty, Radu Grigore, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -14611,7 +14611,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska </t>
+          <t xml:space="preserve">Robert Babuška </t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -14671,7 +14671,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
+          <t xml:space="preserve">Jiří Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -14701,7 +14701,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
+          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olšák, Szymon Stankiewicz </t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -14791,7 +14791,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -14821,7 +14821,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
+          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olšák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -14941,7 +14941,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Inês Lynce </t>
+          <t xml:space="preserve">Mikoláš Janota, Inês Lynce </t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -15031,7 +15031,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hugo Cisneros, Josef Sivic, Tomás Mikolov </t>
+          <t xml:space="preserve">Hugo Cisneros, Josef Sivic, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -15091,7 +15091,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -15181,7 +15181,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Yang, Do Huy Hoang, Tomás Mikolov, Jiawei Han </t>
+          <t xml:space="preserve">Carl Yang, Do Huy Hoang, Tomáš Mikolov, Jiawei Han </t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -15211,7 +15211,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simon Cooksey, Sarah Harris, Mark Batty, Radu Grigore, Mikolás Janota </t>
+          <t xml:space="preserve">Simon Cooksey, Sarah Harris, Mark Batty, Radu Grigore, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -15241,7 +15241,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
+          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olšák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -15271,7 +15271,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radoslav Skoviera, Karla Stépánová, Michael Tesar, Gabriela Sejnova, Jirí Sedlár, Michal Vavrecka, Robert Babuska, Josef Sivic </t>
+          <t xml:space="preserve">Radoslav Skoviera, Karla Stépánová, Michael Tesar, Gabriela Sejnova, Jiří Sedlár, Michal Vavrecka, Robert Babuška, Josef Sivic </t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -15331,7 +15331,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karel Chvalovský, Jan Jakubuv, Martin Suda, Josef Urban </t>
+          <t xml:space="preserve">Karel Chvalovský, Jan Jakubův, Martin Suda, Josef Urban </t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -15361,7 +15361,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Zegklitz, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Jan Zegklitz, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -15391,7 +15391,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Jirí Kubalík, Nicola Ancona, Robert Babuska </t>
+          <t xml:space="preserve">Erik Derner, Jiří Kubalík, Nicola Ancona, Robert Babuška </t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -15421,7 +15421,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -15541,7 +15541,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
+          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olšák, Szymon Stankiewicz </t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -15571,7 +15571,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waren Long, Vadim Markovtsev, Hugo Mougard, Egor Bulychev, Jan Hula </t>
+          <t xml:space="preserve">Waren Long, Vadim Markovtsev, Hugo Mougard, Egor Bulychev, Jan Hůla </t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -15631,7 +15631,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -15811,7 +15811,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Erik Derner, Tim de Bruin, Robert Babuska </t>
+          <t xml:space="preserve">Jonáš Kulhánek, Erik Derner, Tim de Bruin, Robert Babuška </t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -15841,7 +15841,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Yang, Do Huy Hoang, Tomás Mikolov, Jiawei Han </t>
+          <t xml:space="preserve">Carl Yang, Do Huy Hoang, Tomáš Mikolov, Jiawei Han </t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -15871,7 +15871,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piotr Bojanowski, Onur Celebi, Tomás Mikolov, Edouard Grave, Armand Joulin </t>
+          <t xml:space="preserve">Piotr Bojanowski, Onur Celebi, Tomáš Mikolov, Edouard Grave, Armand Joulin </t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -15961,7 +15961,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hugo Cisneros, Josef Sivic, Tomás Mikolov </t>
+          <t xml:space="preserve">Hugo Cisneros, Josef Sivic, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -16051,7 +16051,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák, Cezary Kaliszyk, Josef Urban </t>
+          <t xml:space="preserve">Miroslav Olšák, Cezary Kaliszyk, Josef Urban </t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -16171,7 +16171,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yudha P. Pane, Subramanya Nageshrao, Jens Kober, Robert Babuska </t>
+          <t xml:space="preserve">Yudha P. Pane, Subramanya Nageshrao, Jens Kober, Robert Babuška </t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -16291,7 +16291,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, Miroslav Kubát, Radek Cech, Xinying Chen, David Cíz, Katerina Pelegrinová, Jirí Milicka </t>
+          <t xml:space="preserve">Jan Hůla, Miroslav Kubát, Radek Cech, Xinying Chen, David Cíz, Katerina Pelegrinová, Jiří Milicka </t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -16381,7 +16381,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Van Trung Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olšák, Van Trung Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -16411,7 +16411,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radek Cech, Jan Hula, Miroslav Kubát, Xinying Chen, Jirí Milicka </t>
+          <t xml:space="preserve">Radek Cech, Jan Hůla, Miroslav Kubát, Xinying Chen, Jiří Milicka </t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -16501,7 +16501,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
+          <t xml:space="preserve">Miroslav Kulich, Jiří Kubalík, Libor Preucil </t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -16531,7 +16531,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikolás Janota </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -16561,7 +16561,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -16591,7 +16591,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t xml:space="preserve">Douwe Kiela, Edouard Grave, Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Douwe Kiela, Edouard Grave, Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -16681,7 +16681,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armand Joulin, Piotr Bojanowski, Tomás Mikolov, Hervé Jégou, Edouard Grave </t>
+          <t xml:space="preserve">Armand Joulin, Piotr Bojanowski, Tomáš Mikolov, Hervé Jégou, Edouard Grave </t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -16741,7 +16741,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Jan Jakubův, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -16771,7 +16771,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Jirí Kubalík, Robert Babuska </t>
+          <t xml:space="preserve">Erik Derner, Jiří Kubalík, Robert Babuška </t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -16801,7 +16801,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Jirí Kubalík, Robert Babuska </t>
+          <t xml:space="preserve">Erik Derner, Jiří Kubalík, Robert Babuška </t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -16861,7 +16861,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubuv, Stephan Schulz, Josef Urban </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubův, Stephan Schulz, Josef Urban </t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -16951,7 +16951,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -16981,7 +16981,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolas Janota, Martin Suda </t>
+          <t xml:space="preserve">Mikoláš Janota, Martin Suda </t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -17041,7 +17041,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edouard Grave, Piotr Bojanowski, Prakhar Gupta, Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Edouard Grave, Piotr Bojanowski, Prakhar Gupta, Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -17071,7 +17071,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Edouard Grave, Piotr Bojanowski, Christian Puhrsch, Armand Joulin </t>
+          <t xml:space="preserve">Tomáš Mikolov, Edouard Grave, Piotr Bojanowski, Christian Puhrsch, Armand Joulin </t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -17131,7 +17131,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -17221,7 +17221,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Henryk Michalewski, Miroslav Olsák </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Henryk Michalewski, Miroslav Olšák </t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -17281,7 +17281,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -17341,7 +17341,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Leonardo Leottau, Javier Ruiz-del-Solar, Robert Babuska </t>
+          <t xml:space="preserve">David Leonardo Leottau, Javier Ruiz-del-Solar, Robert Babuška </t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -17401,7 +17401,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -17431,7 +17431,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Douwe Kiela, Edouard Grave, Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Douwe Kiela, Edouard Grave, Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -17491,7 +17491,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubuv, Stephan Schulz, Josef Urban </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel, Jan Jakubův, Stephan Schulz, Josef Urban </t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -17521,7 +17521,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edouard Grave, Piotr Bojanowski, Prakhar Gupta, Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Edouard Grave, Piotr Bojanowski, Prakhar Gupta, Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -17611,7 +17611,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armand Joulin, Piotr Bojanowski, Tomás Mikolov, Edouard Grave </t>
+          <t xml:space="preserve">Armand Joulin, Piotr Bojanowski, Tomáš Mikolov, Edouard Grave </t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -17701,7 +17701,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Henryk Michalewski, Mirek Olsák </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Henryk Michalewski, Mirek Olšák </t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -17821,7 +17821,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samuel R. Bowman, Ellie Pavlick, Edouard Grave, Benjamin Van Durme, Alex Wang, Jan Hula, Patrick Xia, Raghavendra Pappagari, R. Thomas McCoy, Roma Patel, Najoung Kim, Ian Tenney, Yinghui Huang, Katherin Yu, Shuning Jin, Berlin Chen </t>
+          <t xml:space="preserve">Samuel R. Bowman, Ellie Pavlick, Edouard Grave, Benjamin Van Durme, Alex Wang, Jan Hůla, Patrick Xia, Raghavendra Pappagari, R. Thomas McCoy, Roma Patel, Najoung Kim, Ian Tenney, Yinghui Huang, Katherin Yu, Shuning Jin, Berlin Chen </t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -17851,7 +17851,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eduard Alibekov, Jirí Kubalík, Robert Babuska </t>
+          <t xml:space="preserve">Eduard Alibekov, Jiří Kubalík, Robert Babuška </t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -17971,7 +17971,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tim de Bruin, Jens Kober, Karl Tuyls, Robert Babuska </t>
+          <t xml:space="preserve">Tim de Bruin, Jens Kober, Karl Tuyls, Robert Babuška </t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -18001,7 +18001,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tim de Bruin, Jens Kober, Karl Tuyls, Robert Babuska </t>
+          <t xml:space="preserve">Tim de Bruin, Jens Kober, Karl Tuyls, Robert Babuška </t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -18031,7 +18031,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ivan Koryakovskiy, Manuel Kudruss, Heike Vallery, Robert Babuska, Wouter Caarls </t>
+          <t xml:space="preserve">Ivan Koryakovskiy, Manuel Kudruss, Heike Vallery, Robert Babuška, Wouter Caarls </t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -18061,7 +18061,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubův, Antonín Komenda </t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -18151,7 +18151,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim Verbert, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Kim Verbert, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18181,7 +18181,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederik Ruelens, Bert Claessens, Salman Quaiyum, Bart De Schutter, Robert Babuska, Ronnie Belmans </t>
+          <t xml:space="preserve">Frederik Ruelens, Bert Claessens, Salman Quaiyum, Bart De Schutter, Robert Babuška, Ronnie Belmans </t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18211,7 +18211,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Radu Grigore, Vasco Manquinho </t>
+          <t xml:space="preserve">Mikoláš Janota, Radu Grigore, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18241,7 +18241,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -18271,7 +18271,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armand Joulin, Edouard Grave, Piotr Bojanowski, Maximilian Nickel, Tomás Mikolov </t>
+          <t xml:space="preserve">Armand Joulin, Edouard Grave, Piotr Bojanowski, Maximilian Nickel, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -18511,7 +18511,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan-Willem Damsteeg, Subramanya Nageshrao, Robert Babuska </t>
+          <t xml:space="preserve">Jan-Willem Damsteeg, Subramanya Nageshrao, Robert Babuška </t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -18601,7 +18601,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -18631,7 +18631,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armand Joulin, Edouard Grave, Piotr Bojanowski, Tomás Mikolov </t>
+          <t xml:space="preserve">Armand Joulin, Edouard Grave, Piotr Bojanowski, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -18661,7 +18661,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -18691,7 +18691,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Martin Suda, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Martin Suda, Josef Urban </t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -18721,7 +18721,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Baroni, Armand Joulin, Allan Jabri, Germán Kruszewski, Angeliki Lazaridou, Klemen Simonic, Tomás Mikolov </t>
+          <t xml:space="preserve">Marco Baroni, Armand Joulin, Allan Jabri, Germán Kruszewski, Angeliki Lazaridou, Klemen Simonic, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -18751,7 +18751,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yacine Jernite, Edouard Grave, Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Yacine Jernite, Edouard Grave, Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -18781,7 +18781,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ruben Burger, Mukunda Bharatheesha, Marc van Bert, Robert Babuska </t>
+          <t xml:space="preserve">Ruben Burger, Mukunda Bharatheesha, Marc van Bert, Robert Babuška </t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -18811,7 +18811,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Erik Derner, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Erik Derner, Robert Babuška </t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -18841,7 +18841,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -18871,7 +18871,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, Irina Perfilieva, Ali Ahsan Muhummad Muzaheed </t>
+          <t xml:space="preserve">Jan Hůla, Irina Perfilieva, Ali Ahsan Muhummad Muzaheed </t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -18901,7 +18901,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olšák, Trung Van Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -19021,7 +19021,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -19141,7 +19141,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -19201,7 +19201,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Marques-Silva, Mikolás Janota, Carlos Mencía </t>
+          <t xml:space="preserve">João Marques-Silva, Mikoláš Janota, Carlos Mencía </t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -19231,7 +19231,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Baroni, Armand Joulin, Allan Jabri, Germán Kruszewski, Angeliki Lazaridou, Klemen Simonic, Tomás Mikolov </t>
+          <t xml:space="preserve">Marco Baroni, Armand Joulin, Allan Jabri, Germán Kruszewski, Angeliki Lazaridou, Klemen Simonic, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -19261,7 +19261,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -19291,7 +19291,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -19381,7 +19381,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexander G. Ororbia II, Tomás Mikolov, David Reitter </t>
+          <t xml:space="preserve">Alexander G. Ororbia II, Tomáš Mikolov, David Reitter </t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -19441,7 +19441,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolas Janota, Radu Grigore, Vasco Manquinho </t>
+          <t xml:space="preserve">Mikoláš Janota, Radu Grigore, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -19471,7 +19471,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -19501,7 +19501,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armand Joulin, Edouard Grave, Piotr Bojanowski, Maximilian Nickel, Tomás Mikolov </t>
+          <t xml:space="preserve">Armand Joulin, Edouard Grave, Piotr Bojanowski, Maximilian Nickel, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -19561,7 +19561,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Edouard Grave, Piotr Bojanowski, Christian Puhrsch, Armand Joulin </t>
+          <t xml:space="preserve">Tomáš Mikolov, Edouard Grave, Piotr Bojanowski, Christian Puhrsch, Armand Joulin </t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -19591,7 +19591,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim Verbert, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Kim Verbert, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -19621,7 +19621,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim Verbert, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Kim Verbert, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -19711,7 +19711,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexander G. Ororbia II, Tomás Mikolov, David Reitter </t>
+          <t xml:space="preserve">Alexander G. Ororbia II, Tomáš Mikolov, David Reitter </t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -19741,7 +19741,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ivan Koryakovskiy, Manuel Kudruss, Robert Babuska, Wouter Caarls, Christian Kirches, Katja D. Mombaur, Johannes P. Schlöder, Heike Vallery </t>
+          <t xml:space="preserve">Ivan Koryakovskiy, Manuel Kudruss, Robert Babuška, Wouter Caarls, Christian Kirches, Katja D. Mombaur, Johannes P. Schlöder, Heike Vallery </t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -19771,7 +19771,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim Verbert, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Kim Verbert, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -19831,7 +19831,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piotr Bojanowski, Edouard Grave, Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Piotr Bojanowski, Edouard Grave, Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -19861,7 +19861,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tim de Bruin, Kim Verbert, Robert Babuska </t>
+          <t xml:space="preserve">Tim de Bruin, Kim Verbert, Robert Babuška </t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -19891,7 +19891,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederik Ruelens, Bert J. Claessens, Stijn Vandael, Bart De Schutter, Robert Babuska, Ronnie Belmans </t>
+          <t xml:space="preserve">Frederik Ruelens, Bert J. Claessens, Stijn Vandael, Bart De Schutter, Robert Babuška, Ronnie Belmans </t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -19981,7 +19981,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikolas Janota </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -20011,7 +20011,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Martin Svatos, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubův, Martin Svatos, Antonín Komenda </t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -20161,7 +20161,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Christoph M. Wintersteiger </t>
+          <t xml:space="preserve">Mikoláš Janota, Christoph M. Wintersteiger </t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -20221,7 +20221,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eduard Alibekov, Jirí Kubalík, Robert Babuska </t>
+          <t xml:space="preserve">Eduard Alibekov, Jiří Kubalík, Robert Babuška </t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -20251,7 +20251,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelle Munk, Jens Kober, Robert Babuska </t>
+          <t xml:space="preserve">Jelle Munk, Jens Kober, Robert Babuška </t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -20281,7 +20281,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yudha P. Pane, Subramanya Nageshrao, Robert Babuska </t>
+          <t xml:space="preserve">Yudha P. Pane, Subramanya Nageshrao, Robert Babuška </t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -20311,7 +20311,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Armand Joulin, Marco Baroni </t>
+          <t xml:space="preserve">Tomáš Mikolov, Armand Joulin, Marco Baroni </t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -20371,7 +20371,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xujie Si, Xin Zhang, Vasco Manquinho, Mikolás Janota, Alexey Ignatiev, Mayur Naik </t>
+          <t xml:space="preserve">Xujie Si, Xin Zhang, Vasco Manquinho, Mikoláš Janota, Alexey Ignatiev, Mayur Naik </t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -20431,7 +20431,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harish Satyavada, Robert Babuska, Simone Baldi </t>
+          <t xml:space="preserve">Harish Satyavada, Robert Babuška, Simone Baldi </t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -20581,7 +20581,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubův, Antonín Komenda </t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -20641,7 +20641,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wojciech Zaremba, Tomás Mikolov, Armand Joulin, Rob Fergus </t>
+          <t xml:space="preserve">Wojciech Zaremba, Tomáš Mikolov, Armand Joulin, Rob Fergus </t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -20671,7 +20671,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shahrzad Faghih-Roohi, Siamak Hajizadeh, Alfredo Núñez, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Shahrzad Faghih-Roohi, Siamak Hajizadeh, Alfredo Núñez, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -20731,7 +20731,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tim de Bruin, Jens Kober, Karl Tuyls, Robert Babuska </t>
+          <t xml:space="preserve">Tim de Bruin, Jens Kober, Karl Tuyls, Robert Babuška </t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -20881,7 +20881,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -20971,7 +20971,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Leonardo Leottau, Aashish Vatsyayan, Javier Ruiz-del-Solar, Robert Babuska </t>
+          <t xml:space="preserve">David Leonardo Leottau, Aashish Vatsyayan, Javier Ruiz-del-Solar, Robert Babuška </t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -21031,7 +21031,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -21091,7 +21091,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicky Mol, Jan Smisek, Robert Babuska, Andre Schiele </t>
+          <t xml:space="preserve">Nicky Mol, Jan Smisek, Robert Babuška, Andre Schiele </t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -21181,7 +21181,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, William Klieber, João Marques-Silva, Edmund M. Clarke </t>
+          <t xml:space="preserve">Mikoláš Janota, William Klieber, João Marques-Silva, Edmund M. Clarke </t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -21211,7 +21211,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -21271,7 +21271,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hamidreza Modares, Subramanya Nageshrao, Gabriel Alexandre Delgado Lopes, Robert Babuska, Frank L. Lewis </t>
+          <t xml:space="preserve">Hamidreza Modares, Subramanya Nageshrao, Gabriel Alexandre Delgado Lopes, Robert Babuška, Frank L. Lewis </t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -21301,7 +21301,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexey Ignatiev, Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Alexey Ignatiev, Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -21361,7 +21361,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Michael Pinsker, Van Trung Pham </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olšák, Michael Pinsker, Van Trung Pham </t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -21451,7 +21451,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piotr Bojanowski, Edouard Grave, Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Piotr Bojanowski, Edouard Grave, Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -21571,7 +21571,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -21601,7 +21601,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Josef Urban </t>
+          <t xml:space="preserve">Jan Jakubův, Josef Urban </t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -21631,7 +21631,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yacine Jernite, Edouard Grave, Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Yacine Jernite, Edouard Grave, Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -21661,7 +21661,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armand Joulin, Edouard Grave, Piotr Bojanowski, Matthijs Douze, Hervé Jégou, Tomás Mikolov </t>
+          <t xml:space="preserve">Armand Joulin, Edouard Grave, Piotr Bojanowski, Matthijs Douze, Hervé Jégou, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -21691,7 +21691,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armand Joulin, Edouard Grave, Piotr Bojanowski, Tomás Mikolov </t>
+          <t xml:space="preserve">Armand Joulin, Edouard Grave, Piotr Bojanowski, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -21721,7 +21721,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -21901,7 +21901,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Weston, Antoine Bordes, Sumit Chopra, Tomás Mikolov </t>
+          <t xml:space="preserve">Jason Weston, Antoine Bordes, Sumit Chopra, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -21931,7 +21931,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabriel A. D. Lopes, Bart Kersbergen, Bart De Schutter, Ton J. J. van den Boom, Robert Babuska </t>
+          <t xml:space="preserve">Gabriel A. D. Lopes, Bart Kersbergen, Bart De Schutter, Ton J. J. van den Boom, Robert Babuška </t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -21961,7 +21961,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Alexander Daniels, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Alexander Daniels, Robert Babuška </t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -21991,7 +21991,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim Verbert, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Kim Verbert, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -22021,7 +22021,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikolas Janota </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -22081,7 +22081,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolas Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -22201,7 +22201,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolas Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -22261,7 +22261,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda, Michal Pechoucek </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubův, Antonín Komenda, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -22291,7 +22291,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subramanya Nageshrao, Gabriel A. D. Lopes, Dimitri Jeltsema, Robert Babuska </t>
+          <t xml:space="preserve">Subramanya Nageshrao, Gabriel A. D. Lopes, Dimitri Jeltsema, Robert Babuška </t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -22321,7 +22321,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Eduard Alibekov, Jan Zegklitz, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Eduard Alibekov, Jan Zegklitz, Robert Babuška </t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -22351,7 +22351,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esmaeil Najafi, Robert Babuska, Gabriel A. D. Lopes </t>
+          <t xml:space="preserve">Esmaeil Najafi, Robert Babuška, Gabriel A. D. Lopes </t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -22411,7 +22411,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mohammad Shahbazi, Robert Babuska, Gabriel A. D. Lopes </t>
+          <t xml:space="preserve">Mohammad Shahbazi, Robert Babuška, Gabriel A. D. Lopes </t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -22441,7 +22441,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valeriy Balabanov, Jie-Hong Roland Jiang, Mikolas Janota, Magdalena Widl </t>
+          <t xml:space="preserve">Valeriy Balabanov, Jie-Hong Roland Jiang, Mikoláš Janota, Magdalena Widl </t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -22471,7 +22471,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Stephan Schulz, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Stephan Schulz, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -22591,7 +22591,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -22621,7 +22621,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thijs Wensveen, Lucian Busoniu, Robert Babuska </t>
+          <t xml:space="preserve">Thijs Wensveen, Lucian Busoniu, Robert Babuška </t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -22651,7 +22651,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim Verbert, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Kim Verbert, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -22681,7 +22681,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubův, Antonín Komenda </t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -22711,7 +22711,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -22771,7 +22771,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
+          <t xml:space="preserve">Frantisek Hruska, Jiří Kubalík </t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -22801,7 +22801,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Jan Tozicka, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Jakubův, Jan Tozicka, Antonín Komenda </t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -22831,7 +22831,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Jan Tozicka, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Jakubův, Jan Tozicka, Antonín Komenda </t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -22891,7 +22891,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mohammad Shahbazi, Robert Babuska, Gabriel A. D. Lopes </t>
+          <t xml:space="preserve">Mohammad Shahbazi, Robert Babuška, Gabriel A. D. Lopes </t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -22921,7 +22921,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t xml:space="preserve">J. L. Verboom, Sjoerd Tijmons, Christophe De Wagter, B. D. W. Remes, Robert Babuska, Guido C. H. E. de Croon </t>
+          <t xml:space="preserve">J. L. Verboom, Sjoerd Tijmons, Christophe De Wagter, B. D. W. Remes, Robert Babuška, Guido C. H. E. de Croon </t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -22951,7 +22951,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -22981,7 +22981,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -23011,7 +23011,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Marques-Silva, Mikolás Janota, Alexey Ignatiev, António Morgado </t>
+          <t xml:space="preserve">João Marques-Silva, Mikoláš Janota, Alexey Ignatiev, António Morgado </t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -23041,7 +23041,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Robert Babuska </t>
+          <t xml:space="preserve">Jiří Kubalík, Robert Babuška </t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -23071,7 +23071,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -23131,7 +23131,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nikolaj S. Bjørner, Mikolás Janota </t>
+          <t xml:space="preserve">Nikolaj S. Bjørner, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -23161,7 +23161,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nikolaj S. Bjørner, Mikolás Janota, William Klieber </t>
+          <t xml:space="preserve">Nikolaj S. Bjørner, Mikoláš Janota, William Klieber </t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -23251,7 +23251,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -23461,7 +23461,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -23491,7 +23491,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esmaeil Najafi, Robert Babuska, Gabriel A. D. Lopes </t>
+          <t xml:space="preserve">Esmaeil Najafi, Robert Babuška, Gabriel A. D. Lopes </t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -23521,7 +23521,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miguel Neves, Ruben Martins, Mikolás Janota, Inês Lynce, Vasco Manquinho </t>
+          <t xml:space="preserve">Miguel Neves, Ruben Martins, Mikoláš Janota, Inês Lynce, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -23551,7 +23551,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikolás Janota </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -23581,7 +23581,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Inês Lynce, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, Inês Lynce, João Marques-Silva </t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -23611,7 +23611,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piotr Bojanowski, Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Piotr Bojanowski, Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -23731,7 +23731,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armand Joulin, Tomás Mikolov </t>
+          <t xml:space="preserve">Armand Joulin, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -23761,7 +23761,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grégoire Mesnil, Tomás Mikolov, Marc'Aurelio Ranzato, Yoshua Bengio </t>
+          <t xml:space="preserve">Grégoire Mesnil, Tomáš Mikolov, Marc'Aurelio Ranzato, Yoshua Bengio </t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -23791,7 +23791,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Armand Joulin, Marco Baroni </t>
+          <t xml:space="preserve">Tomáš Mikolov, Armand Joulin, Marco Baroni </t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -23821,7 +23821,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Armand Joulin, Sumit Chopra, Michaël Mathieu, Marc'Aurelio Ranzato </t>
+          <t xml:space="preserve">Tomáš Mikolov, Armand Joulin, Sumit Chopra, Michaël Mathieu, Marc'Aurelio Ranzato </t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -23851,7 +23851,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miguel Neves, Ruben Martins, Mikolás Janota, Inês Lynce, Vasco Manquinho </t>
+          <t xml:space="preserve">Miguel Neves, Ruben Martins, Mikoláš Janota, Inês Lynce, Vasco Manquinho </t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -23881,7 +23881,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederik Ruelens, Bert Claessens, Salman Quaiyum, Bart De Schutter, Robert Babuska, Ronnie Belmans </t>
+          <t xml:space="preserve">Frederik Ruelens, Bert Claessens, Salman Quaiyum, Bart De Schutter, Robert Babuška, Ronnie Belmans </t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -23911,7 +23911,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederik Ruelens, Bert Claessens, Stijn Vandael, Bart De Schutter, Robert Babuska, Ronnie Belmans </t>
+          <t xml:space="preserve">Frederik Ruelens, Bert Claessens, Stijn Vandael, Bart De Schutter, Robert Babuška, Ronnie Belmans </t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -23941,7 +23941,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wojciech Zaremba, Tomás Mikolov, Armand Joulin, Rob Fergus </t>
+          <t xml:space="preserve">Wojciech Zaremba, Tomáš Mikolov, Armand Joulin, Rob Fergus </t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -24301,7 +24301,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wouter Wolfslag, Michiel Plooij, Robert Babuska, Martijn Wisse </t>
+          <t xml:space="preserve">Wouter Wolfslag, Michiel Plooij, Robert Babuška, Martijn Wisse </t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -24331,7 +24331,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Karel Durkota, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubův, Karel Durkota, Antonín Komenda </t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -24361,7 +24361,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -24391,7 +24391,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olivier Sprangers, Robert Babuska, Subramanya Nageshrao, Gabriel A. D. Lopes </t>
+          <t xml:space="preserve">Olivier Sprangers, Robert Babuška, Subramanya Nageshrao, Gabriel A. D. Lopes </t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -24511,7 +24511,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jiří Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -24541,7 +24541,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jiří Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -24631,7 +24631,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -24691,7 +24691,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esmaeil Najafi, Gabriel A. D. Lopes, Subramanya Nageshrao, Robert Babuska </t>
+          <t xml:space="preserve">Esmaeil Najafi, Gabriel A. D. Lopes, Subramanya Nageshrao, Robert Babuška </t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -24721,7 +24721,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov </t>
+          <t xml:space="preserve">Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -24751,7 +24751,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubův, Antonín Komenda </t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -24781,7 +24781,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chang Wang, Koen V. Hindriks, Robert Babuska </t>
+          <t xml:space="preserve">Chang Wang, Koen V. Hindriks, Robert Babuška </t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -24811,7 +24811,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Karel Durkota, Antonín Komenda, Michal Pechoucek </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubův, Karel Durkota, Antonín Komenda, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -24841,7 +24841,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chang Wang, Koen V. Hindriks, Robert Babuska </t>
+          <t xml:space="preserve">Chang Wang, Koen V. Hindriks, Robert Babuška </t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -24871,7 +24871,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quoc V. Le, Tomás Mikolov </t>
+          <t xml:space="preserve">Quoc V. Le, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -24901,7 +24901,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexey Ignatiev, Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Alexey Ignatiev, Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -24961,7 +24961,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ciprian Chelba, Tomás Mikolov, Mike Schuster, Qi Ge, Thorsten Brants, Phillipp Koehn, Tony Robinson </t>
+          <t xml:space="preserve">Ciprian Chelba, Tomáš Mikolov, Mike Schuster, Qi Ge, Thorsten Brants, Phillipp Koehn, Tony Robinson </t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -25021,7 +25021,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
+          <t xml:space="preserve">Jiří Kubalík, Michal Snizek </t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -25051,7 +25051,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhe Cong, Bart De Schutter, Mernout Burger, Robert Babuska </t>
+          <t xml:space="preserve">Zhe Cong, Bart De Schutter, Mernout Burger, Robert Babuška </t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -25081,7 +25081,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikolas Janota </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -25201,7 +25201,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil, Herman Geuvers </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil, Herman Geuvers </t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -25321,7 +25321,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Goetz Botterweck, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, Goetz Botterweck, João Marques-Silva </t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -25351,7 +25351,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
+          <t xml:space="preserve">Jiří Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -25381,7 +25381,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anton Belov, Mikolás Janota, Inês Lynce, João Marques-Silva </t>
+          <t xml:space="preserve">Anton Belov, Mikoláš Janota, Inês Lynce, João Marques-Silva </t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -25441,7 +25441,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mohammed I. Abouheaf, Frank L. Lewis, Kyriakos G. Vamvoudakis, Sofie Haesaert, Robert Babuska </t>
+          <t xml:space="preserve">Mohammed I. Abouheaf, Frank L. Lewis, Kyriakos G. Vamvoudakis, Sofie Haesaert, Robert Babuška </t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -25471,7 +25471,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pawel Miroslaw Stano, Arnold J. den Dekker, Zsófia Lendek, Robert Babuska </t>
+          <t xml:space="preserve">Pawel Miroslaw Stano, Arnold J. den Dekker, Zsófia Lendek, Robert Babuška </t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -25561,7 +25561,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofie Haesaert, Robert Babuska, Alessandro Abate </t>
+          <t xml:space="preserve">Sofie Haesaert, Robert Babuška, Alessandro Abate </t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -25591,7 +25591,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -25711,7 +25711,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -25741,7 +25741,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -25771,7 +25771,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jirí Vyskocil, Herman Geuvers </t>
+          <t xml:space="preserve">Cezary Kaliszyk, Josef Urban, Jiří Vyskočil, Herman Geuvers </t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -25801,7 +25801,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quoc V. Le, Tomás Mikolov </t>
+          <t xml:space="preserve">Quoc V. Le, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -25831,7 +25831,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Marques-Silva, Mikolás Janota </t>
+          <t xml:space="preserve">João Marques-Silva, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -25861,7 +25861,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mohammad Norouzi, Tomás Mikolov, Samy Bengio, Yoram Singer, Jonathon Shlens, Andrea Frome, Greg Corrado, Jeffrey Dean </t>
+          <t xml:space="preserve">Mohammad Norouzi, Tomáš Mikolov, Samy Bengio, Yoram Singer, Jonathon Shlens, Andrea Frome, Greg Corrado, Jeffrey Dean </t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -25951,7 +25951,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikolas Janota </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -26011,7 +26011,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolas Janota, Leroy Chew, Olaf Beyersdorff </t>
+          <t xml:space="preserve">Mikoláš Janota, Leroy Chew, Olaf Beyersdorff </t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -26041,7 +26041,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Marques-Silva, Mikolás Janota </t>
+          <t xml:space="preserve">João Marques-Silva, Mikoláš Janota </t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -26161,7 +26161,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Paula Raica, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Zsófia Lendek, Paula Raica, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -26191,7 +26191,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolas Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -26221,7 +26221,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolas Janota, Charles Jordan, Will Klieber, Florian Lonsing, Martina Seidl, Allen Van Gelder </t>
+          <t xml:space="preserve">Mikoláš Janota, Charles Jordan, Will Klieber, Florian Lonsing, Martina Seidl, Allen Van Gelder </t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -26281,7 +26281,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabriel A. D. Lopes, Bart Kersbergen, Ton J. J. van den Boom, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Gabriel A. D. Lopes, Bart Kersbergen, Ton J. J. van den Boom, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -26341,7 +26341,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Alexander Daniels, Rémi Munos, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Alexander Daniels, Rémi Munos, Robert Babuška </t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -26371,7 +26371,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mohammed I. Abouheaf, Frank L. Lewis, Sofie Haesaert, Robert Babuska, Kyriakos G. Vamvoudakis </t>
+          <t xml:space="preserve">Mohammed I. Abouheaf, Frank L. Lewis, Sofie Haesaert, Robert Babuška, Kyriakos G. Vamvoudakis </t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -26401,7 +26401,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selami Beyhan, Zsófia Lendek, Musa Alci, Robert Babuska </t>
+          <t xml:space="preserve">Selami Beyhan, Zsófia Lendek, Musa Alci, Robert Babuška </t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -26431,7 +26431,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. Liu, Bruno Depraetere, Gregory Pinte, Ivo Grondman, Robert Babuska </t>
+          <t xml:space="preserve">M. Liu, Bruno Depraetere, Gregory Pinte, Ivo Grondman, Robert Babuška </t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -26521,7 +26521,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -26701,7 +26701,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Marques-Silva, Mikolás Janota, Anton Belov </t>
+          <t xml:space="preserve">João Marques-Silva, Mikoláš Janota, Anton Belov </t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -26731,7 +26731,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esmaeil Najafi, Gabriel A. D. Lopes, Robert Babuska </t>
+          <t xml:space="preserve">Esmaeil Najafi, Gabriel A. D. Lopes, Robert Babuška </t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -26761,7 +26761,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhe Cong, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Zhe Cong, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -26791,7 +26791,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t xml:space="preserve">William Klieber, Mikolás Janota, João Marques-Silva, Edmund M. Clarke </t>
+          <t xml:space="preserve">William Klieber, Mikoláš Janota, João Marques-Silva, Edmund M. Clarke </t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -26821,7 +26821,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jiří Kubalík </t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -26851,7 +26851,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
+          <t xml:space="preserve">Jaromír Mlejnek, Jiří Kubalík </t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -26881,7 +26881,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t xml:space="preserve">Razvan Pascanu, Tomás Mikolov, Yoshua Bengio </t>
+          <t xml:space="preserve">Razvan Pascanu, Tomáš Mikolov, Yoshua Bengio </t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -26911,7 +26911,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhe Cong, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Zhe Cong, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -26941,7 +26941,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jurren Pen, Wouter Caarls, Martijn Wisse, Robert Babuska </t>
+          <t xml:space="preserve">Jurren Pen, Wouter Caarls, Martijn Wisse, Robert Babuška </t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -26971,7 +26971,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Marques-Silva, Federico Heras, Mikolás Janota, Alessandro Previti, Anton Belov </t>
+          <t xml:space="preserve">João Marques-Silva, Federico Heras, Mikoláš Janota, Alessandro Previti, Anton Belov </t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -27001,7 +27001,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jiří Kubalík </t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -27031,7 +27031,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ivo Grondman, Hao Xu, Sarangapani Jagannathan, Robert Babuska </t>
+          <t xml:space="preserve">Ivo Grondman, Hao Xu, Sarangapani Jagannathan, Robert Babuška </t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
@@ -27061,7 +27061,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chang Wang, Koen V. Hindriks, Robert Babuska </t>
+          <t xml:space="preserve">Chang Wang, Koen V. Hindriks, Robert Babuška </t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -27151,7 +27151,7 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Radu Grigore, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, Radu Grigore, João Marques-Silva </t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
@@ -27271,7 +27271,7 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Wen-tau Yih, Geoffrey Zweig </t>
+          <t xml:space="preserve">Tomáš Mikolov, Wen-tau Yih, Geoffrey Zweig </t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -27301,7 +27301,7 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alisa Zhila, Wen-tau Yih, Christopher Meek, Geoffrey Zweig, Tomás Mikolov </t>
+          <t xml:space="preserve">Alisa Zhila, Wen-tau Yih, Christopher Meek, Geoffrey Zweig, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -27331,7 +27331,7 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrea Frome, Gregory S. Corrado, Jonathon Shlens, Samy Bengio, Jeffrey Dean, Marc'Aurelio Ranzato, Tomás Mikolov </t>
+          <t xml:space="preserve">Andrea Frome, Gregory S. Corrado, Jonathon Shlens, Samy Bengio, Jeffrey Dean, Marc'Aurelio Ranzato, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -27361,7 +27361,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Ilya Sutskever, Kai Chen, Gregory S. Corrado, Jeffrey Dean </t>
+          <t xml:space="preserve">Tomáš Mikolov, Ilya Sutskever, Kai Chen, Gregory S. Corrado, Jeffrey Dean </t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -27391,7 +27391,7 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mohammad Shahbazi, Gabriel A. D. Lopes, Robert Babuska </t>
+          <t xml:space="preserve">Mohammad Shahbazi, Gabriel A. D. Lopes, Robert Babuška </t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -27421,7 +27421,7 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t xml:space="preserve">F. Zhang, Gabriel Alexandre Delgado Lopes, Robert Babuska </t>
+          <t xml:space="preserve">F. Zhang, Gabriel Alexandre Delgado Lopes, Robert Babuška </t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -27451,7 +27451,7 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexey Ignatiev, Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Alexey Ignatiev, Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -27481,7 +27481,7 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -27511,7 +27511,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrea Simonetto, Tamás Keviczky, Robert Babuska </t>
+          <t xml:space="preserve">Andrea Simonetto, Tamás Keviczky, Robert Babuška </t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -27541,7 +27541,7 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pawel Miroslaw Stano, Zsófia Lendek, Robert Babuska </t>
+          <t xml:space="preserve">Pawel Miroslaw Stano, Zsófia Lendek, Robert Babuška </t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -27571,7 +27571,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ciprian Chelba, Tomás Mikolov, Mike Schuster, Qi Ge, Thorsten Brants, Phillipp Koehn </t>
+          <t xml:space="preserve">Ciprian Chelba, Tomáš Mikolov, Mike Schuster, Qi Ge, Thorsten Brants, Phillipp Koehn </t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -27601,7 +27601,7 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Radu Grigore, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, Radu Grigore, João Marques-Silva </t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -27751,7 +27751,7 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Quoc V. Le, Ilya Sutskever </t>
+          <t xml:space="preserve">Tomáš Mikolov, Quoc V. Le, Ilya Sutskever </t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
@@ -27781,7 +27781,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Ilya Sutskever, Kai Chen, Greg Corrado, Jeffrey Dean </t>
+          <t xml:space="preserve">Tomáš Mikolov, Ilya Sutskever, Kai Chen, Greg Corrado, Jeffrey Dean </t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -27901,7 +27901,7 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Kai Chen, Greg Corrado, Jeffrey Dean </t>
+          <t xml:space="preserve">Tomáš Mikolov, Kai Chen, Greg Corrado, Jeffrey Dean </t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -27991,7 +27991,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -28111,7 +28111,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anoop Deoras, Tomás Mikolov, Stefan Kombrink, Kenneth Church </t>
+          <t xml:space="preserve">Anoop Deoras, Tomáš Mikolov, Stefan Kombrink, Kenneth Church </t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -28141,7 +28141,7 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pawel Stano, Zsófia Lendek, Jelmer Braaksma, Robert Babuska, Cees de Keizer, Arnold J. den Dekker </t>
+          <t xml:space="preserve">Pawel Stano, Zsófia Lendek, Jelmer Braaksma, Robert Babuška, Cees de Keizer, Arnold J. den Dekker </t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -28171,7 +28171,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Alessandro Lazaric, Mohammad Ghavamzadeh, Rémi Munos, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Lucian Busoniu, Alessandro Lazaric, Mohammad Ghavamzadeh, Rémi Munos, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -28201,7 +28201,7 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zulkifli Hidayat, Alfredo Núñez, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zulkifli Hidayat, Alfredo Núñez, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -28231,7 +28231,7 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
+          <t xml:space="preserve">Kamil Matousek, Jiří Kubalík, Martin Necaský, Peter Vojtás </t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -28321,7 +28321,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mohsen Alirezaei, Ton J. J. van den Boom, Robert Babuska </t>
+          <t xml:space="preserve">Mohsen Alirezaei, Ton J. J. van den Boom, Robert Babuška </t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -28501,7 +28501,7 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ivo Grondman, Lucian Busoniu, Robert Babuska </t>
+          <t xml:space="preserve">Ivo Grondman, Lucian Busoniu, Robert Babuška </t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -28531,7 +28531,7 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anton Belov, Mikolás Janota, Inês Lynce, João Marques-Silva </t>
+          <t xml:space="preserve">Anton Belov, Mikoláš Janota, Inês Lynce, João Marques-Silva </t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
@@ -28561,7 +28561,7 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huan Chen, Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Huan Chen, Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -28591,7 +28591,7 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
+          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jiří Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
@@ -28621,7 +28621,7 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jiří Kubalík </t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -28651,7 +28651,7 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t xml:space="preserve">S. Bindiganavile Nagesh, Zsófia Lendek, Amol A. Khalate, Robert Babuska </t>
+          <t xml:space="preserve">S. Bindiganavile Nagesh, Zsófia Lendek, Amol A. Khalate, Robert Babuška </t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
@@ -28681,7 +28681,7 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan Kombrink, Tomás Mikolov, Martin Karafiát, Lukás Burget </t>
+          <t xml:space="preserve">Stefan Kombrink, Tomáš Mikolov, Martin Karafiát, Lukás Burget </t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -28711,7 +28711,7 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucas Bordeaux, Mikolás Janota, João Marques-Silva, Pierre Marquis </t>
+          <t xml:space="preserve">Lucas Bordeaux, Mikoláš Janota, João Marques-Silva, Pierre Marquis </t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
@@ -28801,7 +28801,7 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, William Klieber, João Marques-Silva, Edmund M. Clarke </t>
+          <t xml:space="preserve">Mikoláš Janota, William Klieber, João Marques-Silva, Edmund M. Clarke </t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -28831,7 +28831,7 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Geoffrey Zweig </t>
+          <t xml:space="preserve">Tomáš Mikolov, Geoffrey Zweig </t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
@@ -28921,7 +28921,7 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrea Simonetto, Tamás Keviczky, Robert Babuska </t>
+          <t xml:space="preserve">Andrea Simonetto, Tamás Keviczky, Robert Babuška </t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -28951,7 +28951,7 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josef Urban, Jirí Vyskocil </t>
+          <t xml:space="preserve">Josef Urban, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
@@ -28981,7 +28981,7 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t xml:space="preserve">Razvan Pascanu, Tomás Mikolov, Yoshua Bengio </t>
+          <t xml:space="preserve">Razvan Pascanu, Tomáš Mikolov, Yoshua Bengio </t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
@@ -29041,7 +29041,7 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olivier Sprangers, Gabriel A. D. Lopes, Robert Babuska </t>
+          <t xml:space="preserve">Olivier Sprangers, Gabriel A. D. Lopes, Robert Babuška </t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
@@ -29071,7 +29071,7 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabriel Alexandre Delgado Lopes, Bart Kersbergen, Bart De Schutter, Ton J. J. van den Boom, Robert Babuska </t>
+          <t xml:space="preserve">Gabriel Alexandre Delgado Lopes, Bart Kersbergen, Bart De Schutter, Ton J. J. van den Boom, Robert Babuška </t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
@@ -29101,7 +29101,7 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Petr Posík, Jiří Kubalík </t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -29161,7 +29161,7 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Inês Lynce, Vasco Manquinho, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, Inês Lynce, Vasco Manquinho, João Marques-Silva </t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
@@ -29221,7 +29221,7 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sander Adam, Lucian Busoniu, Robert Babuska </t>
+          <t xml:space="preserve">Sander Adam, Lucian Busoniu, Robert Babuška </t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
@@ -29251,7 +29251,7 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ivo Grondman, Lucian Busoniu, Gabriel A. D. Lopes, Robert Babuska </t>
+          <t xml:space="preserve">Ivo Grondman, Lucian Busoniu, Gabriel A. D. Lopes, Robert Babuška </t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
@@ -29281,7 +29281,7 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ivo Grondman, Maarten Vaandrager, Lucian Busoniu, Robert Babuska, Erik Schuitema </t>
+          <t xml:space="preserve">Ivo Grondman, Maarten Vaandrager, Lucian Busoniu, Robert Babuška, Erik Schuitema </t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
@@ -29311,7 +29311,7 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shouyi Wang, Wanpracha Art Chaovalitwongse, Robert Babuska </t>
+          <t xml:space="preserve">Shouyi Wang, Wanpracha Art Chaovalitwongse, Robert Babuška </t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
@@ -29341,7 +29341,7 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Thierry-Marie Guerra, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zsófia Lendek, Thierry-Marie Guerra, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
@@ -29371,7 +29371,7 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
@@ -29401,7 +29401,7 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Rémi Munos, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Rémi Munos, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
@@ -29431,7 +29431,7 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrea Simonetto, Tamás Keviczky, Robert Babuska </t>
+          <t xml:space="preserve">Andrea Simonetto, Tamás Keviczky, Robert Babuška </t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
@@ -29461,7 +29461,7 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pawel Stano, Zsófia Lendek, Robert Babuska </t>
+          <t xml:space="preserve">Pawel Stano, Zsófia Lendek, Robert Babuška </t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -29491,7 +29491,7 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Anoop Deoras, Daniel Povey, Lukás Burget, Jan Cernocký </t>
+          <t xml:space="preserve">Tomáš Mikolov, Anoop Deoras, Daniel Povey, Lukás Burget, Jan Cernocký </t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
@@ -29581,7 +29581,7 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
+          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomáš Skopal, Kamil Matousek, Jiří Kubalík, Ota Novotný, Milos Maryska </t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -29611,7 +29611,7 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selami Beyhan, Zsófia Lendek, Robert Babuska, Martijn Wisse, Musa Alci </t>
+          <t xml:space="preserve">Selami Beyhan, Zsófia Lendek, Robert Babuška, Martijn Wisse, Musa Alci </t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
@@ -29641,7 +29641,7 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amol A. Khalate, Benoit Bayon, Xavier Bombois, Gérard Scorletti, Robert Babuska </t>
+          <t xml:space="preserve">Amol A. Khalate, Benoit Bayon, Xavier Bombois, Gérard Scorletti, Robert Babuška </t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -29671,7 +29671,7 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabriel Alexandre Delgado Lopes, Bart Kersbergen, Ton J. J. van den Boom, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Gabriel Alexandre Delgado Lopes, Bart Kersbergen, Ton J. J. van den Boom, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
@@ -29701,7 +29701,7 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
@@ -29731,7 +29731,7 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anoop Deoras, Tomás Mikolov, Kenneth Church </t>
+          <t xml:space="preserve">Anoop Deoras, Tomáš Mikolov, Kenneth Church </t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
@@ -29761,7 +29761,7 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zulkifli Hidayat, Robert Babuska, Bart De Schutter, Alfredo Núñez </t>
+          <t xml:space="preserve">Zulkifli Hidayat, Robert Babuška, Bart De Schutter, Alfredo Núñez </t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -29791,7 +29791,7 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jiří Kubalík </t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
@@ -29851,7 +29851,7 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anoop Deoras, Tomás Mikolov, Stefan Kombrink, Martin Karafiát, Sanjeev Khudanpur </t>
+          <t xml:space="preserve">Anoop Deoras, Tomáš Mikolov, Stefan Kombrink, Martin Karafiát, Sanjeev Khudanpur </t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
@@ -29881,7 +29881,7 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Stefan Kombrink, Lukás Burget, Jan Cernocký, Sanjeev Khudanpur </t>
+          <t xml:space="preserve">Tomáš Mikolov, Stefan Kombrink, Lukás Burget, Jan Cernocký, Sanjeev Khudanpur </t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -29911,7 +29911,7 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan Kombrink, Tomás Mikolov, Martin Karafiát, Lukás Burget </t>
+          <t xml:space="preserve">Stefan Kombrink, Tomáš Mikolov, Martin Karafiát, Lukás Burget </t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
@@ -29941,7 +29941,7 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Anoop Deoras, Stefan Kombrink, Lukás Burget, Jan Cernocký </t>
+          <t xml:space="preserve">Tomáš Mikolov, Anoop Deoras, Stefan Kombrink, Lukás Burget, Jan Cernocký </t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -29971,7 +29971,7 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bart Kersbergen, Gabriel A. D. Lopes, Ton J. J. van den Boom, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Bart Kersbergen, Gabriel A. D. Lopes, Ton J. J. van den Boom, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
@@ -30061,7 +30061,7 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhe Cong, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Zhe Cong, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -30091,7 +30091,7 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
@@ -30271,7 +30271,7 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zulkifli Hidayat, Robert Babuska, Bart De Schutter, Alfredo Núñez </t>
+          <t xml:space="preserve">Zulkifli Hidayat, Robert Babuška, Bart De Schutter, Alfredo Núñez </t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
@@ -30301,7 +30301,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -30361,7 +30361,7 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josef Urban, Jirí Vyskocil, Petr Stepánek </t>
+          <t xml:space="preserve">Josef Urban, Jiří Vyskočil, Petr Stepánek </t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
@@ -30391,7 +30391,7 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Petr Buryan, Jiří Kubalík </t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
@@ -30421,7 +30421,7 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Thomas Kremmel, Jiří Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
@@ -30601,7 +30601,7 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huan Chen, Mikolás Janota, João Marques-Silva </t>
+          <t xml:space="preserve">Huan Chen, Mikoláš Janota, João Marques-Silva </t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
@@ -30631,7 +30631,7 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zsófia Lendek, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
@@ -30661,7 +30661,7 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Jimmy Lauber, Thierry-Marie Guerra, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zsófia Lendek, Jimmy Lauber, Thierry-Marie Guerra, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -30751,7 +30751,7 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
@@ -30781,7 +30781,7 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pawel Stano, Zsófia Lendek, Robert Babuska, Jelmer Braaksma, Cees de Keizer </t>
+          <t xml:space="preserve">Pawel Stano, Zsófia Lendek, Robert Babuška, Jelmer Braaksma, Cees de Keizer </t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -30871,7 +30871,7 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
@@ -30901,7 +30901,7 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amol A. Khalate, Xavier Bombois, Robert Babuska, Herman Wijshoff, René Waarsing </t>
+          <t xml:space="preserve">Amol A. Khalate, Xavier Bombois, Robert Babuška, Herman Wijshoff, René Waarsing </t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -30931,7 +30931,7 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zsófia Lendek, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
@@ -31021,7 +31021,7 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelmer van Ast, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Jelmer van Ast, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -31051,7 +31051,7 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrea Simonetto, Tamás Keviczky, Robert Babuska </t>
+          <t xml:space="preserve">Andrea Simonetto, Tamás Keviczky, Robert Babuška </t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
@@ -31081,7 +31081,7 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Marques-Silva, Mikolás Janota, Inês Lynce </t>
+          <t xml:space="preserve">João Marques-Silva, Mikoláš Janota, Inês Lynce </t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -31141,7 +31141,7 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ana Belén Cara, Zsófia Lendek, Robert Babuska, Héctor Pomares, Ignacio Rojas </t>
+          <t xml:space="preserve">Ana Belén Cara, Zsófia Lendek, Robert Babuška, Héctor Pomares, Ignacio Rojas </t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -31171,7 +31171,7 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Thierry-Marie Guerra, Robert Babuska </t>
+          <t xml:space="preserve">Zsófia Lendek, Thierry-Marie Guerra, Robert Babuška </t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
@@ -31201,7 +31201,7 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Petr Buryan, Jiří Kubalík </t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -31231,7 +31231,7 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Thomas Kremmel, Jiří Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
@@ -31261,7 +31261,7 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jiří Kubalík </t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -31291,7 +31291,7 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jiří Kubalík </t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
@@ -31321,7 +31321,7 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
+          <t xml:space="preserve">Jiří Kubalík, Petr Buryan, Libor Wagner </t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -31351,7 +31351,7 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Petr Posík, Jiří Kubalík </t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
@@ -31411,7 +31411,7 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrea Simonetto, Tamás Keviczky, Robert Babuska </t>
+          <t xml:space="preserve">Andrea Simonetto, Tamás Keviczky, Robert Babuška </t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
@@ -31441,7 +31441,7 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Martin Karafiát, Lukás Burget, Jan Cernocký, Sanjeev Khudanpur </t>
+          <t xml:space="preserve">Tomáš Mikolov, Martin Karafiát, Lukás Burget, Jan Cernocký, Sanjeev Khudanpur </t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -31471,7 +31471,7 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t xml:space="preserve">David van der Lijn, Gabriel A. D. Lopes, Robert Babuska </t>
+          <t xml:space="preserve">David van der Lijn, Gabriel A. D. Lopes, Robert Babuška </t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
@@ -31501,7 +31501,7 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Schuitema, Lucian Busoniu, Robert Babuska, Pieter Jonker </t>
+          <t xml:space="preserve">Erik Schuitema, Lucian Busoniu, Robert Babuška, Pieter Jonker </t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -31531,7 +31531,7 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diogo Alves, Jelmer van Ast, Zhe Cong, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Diogo Alves, Jelmer van Ast, Zhe Cong, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
@@ -31561,7 +31561,7 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zulkifli Hidayat, Zsófia Lendek, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zulkifli Hidayat, Zsófia Lendek, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -31591,7 +31591,7 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Radu Grigore, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, Radu Grigore, João Marques-Silva </t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
@@ -31651,7 +31651,7 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Vyskocil, David Stanovský, Josef Urban </t>
+          <t xml:space="preserve">Jiří Vyskočil, David Stanovský, Josef Urban </t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
@@ -31681,7 +31681,7 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zdenek Jancik, Oldrich Plchot, Niko Brümmer, Lukás Burget, Ondrej Glembek, Valiantsina Hubeika, Martin Karafiát, Pavel Matejka, Tomás Mikolov, Albert Strasheim, Jan Cernocký </t>
+          <t xml:space="preserve">Zdenek Jancik, Oldrich Plchot, Niko Brümmer, Lukás Burget, Ondrej Glembek, Valiantsina Hubeika, Martin Karafiát, Pavel Matejka, Tomáš Mikolov, Albert Strasheim, Jan Cernocký </t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -31711,7 +31711,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Oldrich Plchot, Ondrej Glembek, Lukás Burget, Jan Cernocký </t>
+          <t xml:space="preserve">Tomáš Mikolov, Oldrich Plchot, Ondrej Glembek, Lukás Burget, Jan Cernocký </t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
@@ -31741,7 +31741,7 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Goetz Botterweck, Radu Grigore, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, Goetz Botterweck, Radu Grigore, João Marques-Silva </t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
@@ -31771,7 +31771,7 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, J. B. Wells </t>
+          <t xml:space="preserve">Jan Jakubův, J. B. Wells </t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
@@ -31801,7 +31801,7 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabriel A. D. Lopes, Ton J. J. van den Boom, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Gabriel A. D. Lopes, Ton J. J. van den Boom, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -31831,7 +31831,7 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
@@ -31861,7 +31861,7 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, J. B. Wells </t>
+          <t xml:space="preserve">Jan Jakubův, J. B. Wells </t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -31981,7 +31981,7 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva, Radu Grigore </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva, Radu Grigore </t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -32011,7 +32011,7 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ana Belén Cara, Héctor Pomares, Ignacio Rojas, Zsófia Lendek, Robert Babuska </t>
+          <t xml:space="preserve">Ana Belén Cara, Héctor Pomares, Ignacio Rojas, Zsófia Lendek, Robert Babuška </t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
@@ -32041,7 +32041,7 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Jimmy Lauber, Thierry-Marie Guerra, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zsófia Lendek, Jimmy Lauber, Thierry-Marie Guerra, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -32071,7 +32071,7 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
+          <t xml:space="preserve">Jiří Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
@@ -32101,7 +32101,7 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv </t>
+          <t xml:space="preserve">Jan Jakubův </t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
@@ -32131,7 +32131,7 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska, Frans C. A. Groen </t>
+          <t xml:space="preserve">Robert Babuška, Frans C. A. Groen </t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
@@ -32161,7 +32161,7 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelmer Marinus van Ast, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Jelmer Marinus van Ast, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -32191,7 +32191,7 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
@@ -32221,7 +32221,7 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -32251,7 +32251,7 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelmer van Ast, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Jelmer van Ast, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
@@ -32281,7 +32281,7 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ö. Aydin Tekin, Robert Babuska, Tetsuo Tomiyama, Bart De Schutter </t>
+          <t xml:space="preserve">Ö. Aydin Tekin, Robert Babuška, Tetsuo Tomiyama, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
@@ -32371,7 +32371,7 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alaa F. Sheta, Ertan Öznergiz, M. A. Abdelrahman, Robert Babuska </t>
+          <t xml:space="preserve">Alaa F. Sheta, Ertan Öznergiz, M. A. Abdelrahman, Robert Babuška </t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
@@ -32401,7 +32401,7 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Fintan Fairmichael, Viliam Holub, Radu Grigore, Julien Charles, Dermot Cochran, Joseph R. Kiniry </t>
+          <t xml:space="preserve">Mikoláš Janota, Fintan Fairmichael, Viliam Holub, Radu Grigore, Julien Charles, Dermot Cochran, Joseph R. Kiniry </t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
@@ -32431,7 +32431,7 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jiří Kubalík </t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
@@ -32461,7 +32461,7 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jiří Kubalík </t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
@@ -32491,7 +32491,7 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jiří Kubalík </t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
@@ -32521,7 +32521,7 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomás Mikolov, Jirí Kopecký, Lukás Burget, Ondrej Glembek, Jan Cernocký </t>
+          <t xml:space="preserve">Tomáš Mikolov, Jiří Kopecký, Lukás Burget, Ondrej Glembek, Jan Cernocký </t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
@@ -32551,7 +32551,7 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
+          <t xml:space="preserve">Petr Buryan, Jiří Kubalík, Katsumi Inoue </t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
@@ -32611,7 +32611,7 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabriel A. D. Lopes, Robert Babuska, Bart De Schutter, Ton J. J. van den Boom </t>
+          <t xml:space="preserve">Gabriel A. D. Lopes, Robert Babuška, Bart De Schutter, Ton J. J. van den Boom </t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
@@ -32701,7 +32701,7 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goetz Botterweck, Mikolás Janota, Denny Schneeweiss </t>
+          <t xml:space="preserve">Goetz Botterweck, Mikoláš Janota, Denny Schneeweiss </t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
@@ -32761,7 +32761,7 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, João Marques-Silva, Radu Grigore </t>
+          <t xml:space="preserve">Mikoláš Janota, João Marques-Silva, Radu Grigore </t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
@@ -32791,7 +32791,7 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Goetz Botterweck, Radu Grigore, João Marques-Silva </t>
+          <t xml:space="preserve">Mikoláš Janota, Goetz Botterweck, Radu Grigore, João Marques-Silva </t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
@@ -32821,7 +32821,7 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelmer Marinus van Ast, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Jelmer Marinus van Ast, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
@@ -32851,7 +32851,7 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zsófia Lendek, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
@@ -32881,7 +32881,7 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josef Urban, Geoff Sutcliffe, Petr Pudlák, Jirí Vyskocil </t>
+          <t xml:space="preserve">Josef Urban, Geoff Sutcliffe, Petr Pudlák, Jiří Vyskočil </t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -32911,7 +32911,7 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelmer van Ast, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Jelmer van Ast, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
@@ -32941,7 +32941,7 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelmer van Ast, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Jelmer van Ast, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
@@ -32971,7 +32971,7 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
+          <t xml:space="preserve">Jiří Kubalík, Richard Mordinyi, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
@@ -33001,7 +33001,7 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Goetz Botterweck </t>
+          <t xml:space="preserve">Mikoláš Janota, Goetz Botterweck </t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
@@ -33031,7 +33031,7 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
@@ -33061,7 +33061,7 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zsófia Lendek, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
@@ -33091,7 +33091,7 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrej Glembek, Pavel Matejka, Lukás Burget, Tomás Mikolov </t>
+          <t xml:space="preserve">Ondrej Glembek, Pavel Matejka, Lukás Burget, Tomáš Mikolov </t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
@@ -33121,7 +33121,7 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pavel Matejka, Lukás Burget, Ondrej Glembek, Petr Schwarz, Valiantsina Hubeika, Michal Fapso, Tomás Mikolov, Oldrich Plchot, Jan Cernocký </t>
+          <t xml:space="preserve">Pavel Matejka, Lukás Burget, Ondrej Glembek, Petr Schwarz, Valiantsina Hubeika, Michal Fapso, Tomáš Mikolov, Oldrich Plchot, Jan Cernocký </t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
@@ -33181,7 +33181,7 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Victoria Kuzina, Andrzej Wasowski </t>
+          <t xml:space="preserve">Mikoláš Janota, Victoria Kuzina, Andrzej Wasowski </t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
@@ -33211,7 +33211,7 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota </t>
+          <t xml:space="preserve">Mikoláš Janota </t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
@@ -33241,7 +33241,7 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domenico Bellomo, David Naso, Robert Babuska </t>
+          <t xml:space="preserve">Domenico Bellomo, David Naso, Robert Babuška </t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
@@ -33271,7 +33271,7 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zsófia Lendek, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
@@ -33421,7 +33421,7 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska, Ebrahim Mamdani </t>
+          <t xml:space="preserve">Robert Babuška, Ebrahim Mamdani </t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
@@ -33451,7 +33451,7 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Lucian Busoniu, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
@@ -33481,7 +33481,7 @@
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
+          <t xml:space="preserve">Jiří Kubalík, Richard Mordinyi </t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
@@ -33511,7 +33511,7 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
@@ -33601,7 +33601,7 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Damien Ernst, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
@@ -33631,7 +33631,7 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zsófia Lendek, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Zsófia Lendek, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
@@ -33721,7 +33721,7 @@
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Radu Grigore, Michal Moskal </t>
+          <t xml:space="preserve">Mikoláš Janota, Radu Grigore, Michal Moskal </t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
@@ -33751,7 +33751,7 @@
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikolás Janota, Joseph Kiniry </t>
+          <t xml:space="preserve">Mikoláš Janota, Joseph Kiniry </t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
@@ -33811,7 +33811,7 @@
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska </t>
+          <t xml:space="preserve">Robert Babuška </t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
@@ -33841,7 +33841,7 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska, Zsófia Lendek, Jelmer Braaksma, Cees de Keizer </t>
+          <t xml:space="preserve">Robert Babuška, Zsófia Lendek, Jelmer Braaksma, Cees de Keizer </t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
@@ -33931,7 +33931,7 @@
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jiří Kubalík </t>
         </is>
       </c>
       <c r="B1118" t="inlineStr">
@@ -33961,7 +33961,7 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
+          <t xml:space="preserve">Jiří Kubalík, Jan Faigl </t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
@@ -33991,7 +33991,7 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska, Jelmer van Ast, Samir Mesic </t>
+          <t xml:space="preserve">Robert Babuška, Jelmer van Ast, Samir Mesic </t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
@@ -34021,7 +34021,7 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Oosterom, Robert Babuska </t>
+          <t xml:space="preserve">Marcel Oosterom, Robert Babuška </t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
@@ -34051,7 +34051,7 @@
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Lucian Busoniu, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
@@ -34081,7 +34081,7 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
@@ -34111,7 +34111,7 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelmer van Ast, Robert Babuska </t>
+          <t xml:space="preserve">Jelmer van Ast, Robert Babuška </t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
@@ -34141,7 +34141,7 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shouyi Wang, Jelmer Braaksma, Robert Babuska, Daan G. E. Hobbelen </t>
+          <t xml:space="preserve">Shouyi Wang, Jelmer Braaksma, Robert Babuška, Daan G. E. Hobbelen </t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
@@ -34171,7 +34171,7 @@
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andreas Hegyi, Daniela Girimonte, Robert Babuska, Bart De Schutter </t>
+          <t xml:space="preserve">Andreas Hegyi, Daniela Girimonte, Robert Babuška, Bart De Schutter </t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
@@ -34231,7 +34231,7 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
+          <t xml:space="preserve">Jiří Kubalík, Petr Posík, Jan Herold </t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
@@ -34261,7 +34261,7 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wolfgang A. Halang, Ricardo Sanz, Robert Babuska, Hubert Roth </t>
+          <t xml:space="preserve">Wolfgang A. Halang, Ricardo Sanz, Robert Babuška, Hubert Roth </t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
@@ -34501,7 +34501,7 @@
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koen Maertens, Josse De Baerdemaeker, Robert Babuska </t>
+          <t xml:space="preserve">Koen Maertens, Josse De Baerdemaeker, Robert Babuška </t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
@@ -34531,7 +34531,7 @@
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucian Busoniu, Bart De Schutter, Robert Babuska </t>
+          <t xml:space="preserve">Lucian Busoniu, Bart De Schutter, Robert Babuška </t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
@@ -34591,7 +34591,7 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
+          <t xml:space="preserve">Jan Suchý, Jiří Kubalík </t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
@@ -34621,7 +34621,7 @@
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domenico Bellomo, David Naso, Robert Babuska </t>
+          <t xml:space="preserve">Domenico Bellomo, David Naso, Robert Babuška </t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
@@ -34651,7 +34651,7 @@
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xiangping Meng, Robert Babuska, Lucian Busoniu, Yu Chen, Wanyu Tan </t>
+          <t xml:space="preserve">Xiangping Meng, Robert Babuška, Lucian Busoniu, Yu Chen, Wanyu Tan </t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
@@ -34741,7 +34741,7 @@
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
+          <t xml:space="preserve">Jiří Kléma, Jiří Kubalík, Lenka Lhotská </t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
@@ -34771,7 +34771,7 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antonio Sala, Thierry-Marie Guerra, Robert Babuska </t>
+          <t xml:space="preserve">Antonio Sala, Thierry-Marie Guerra, Robert Babuška </t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
@@ -34801,7 +34801,7 @@
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexander Breijs, J. Ben Klaassens, Robert Babuska </t>
+          <t xml:space="preserve">Alexander Breijs, J. Ben Klaassens, Robert Babuška </t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
@@ -34861,7 +34861,7 @@
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t xml:space="preserve">János Abonyi, Robert Babuska </t>
+          <t xml:space="preserve">János Abonyi, Robert Babuška </t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
@@ -34891,7 +34891,7 @@
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniela Girimonte, Robert Babuska, János Abonyi </t>
+          <t xml:space="preserve">Daniela Girimonte, Robert Babuška, János Abonyi </t>
         </is>
       </c>
       <c r="B1150" t="inlineStr">
@@ -34921,7 +34921,7 @@
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
+          <t xml:space="preserve">Jiří Kubalík, Jiří Kléma, Miroslav Kulich </t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
@@ -34951,7 +34951,7 @@
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domenico Bellomo, David Naso, Robert Babuska </t>
+          <t xml:space="preserve">Domenico Bellomo, David Naso, Robert Babuška </t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
@@ -34981,7 +34981,7 @@
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jelmer Braaksma, J. Ben Klaassens, Robert Babuska, Cees de Keizer </t>
+          <t xml:space="preserve">Jelmer Braaksma, J. Ben Klaassens, Robert Babuška, Cees de Keizer </t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
@@ -35011,7 +35011,7 @@
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
+          <t xml:space="preserve">Jiří Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
@@ -35041,7 +35041,7 @@
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
+          <t xml:space="preserve">Milan Rollo, Petr Novák, Jiří Kubalík, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
@@ -35101,7 +35101,7 @@
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t xml:space="preserve">János Abonyi, Balazs Feil, Sándor Zoltán Németh, Peter Arva, Robert Babuska </t>
+          <t xml:space="preserve">János Abonyi, Balazs Feil, Sándor Zoltán Németh, Peter Arva, Robert Babuška </t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
@@ -35131,7 +35131,7 @@
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniela Girimonte, Robert Babuska </t>
+          <t xml:space="preserve">Daniela Girimonte, Robert Babuška </t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
@@ -35281,7 +35281,7 @@
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stanimir Mollov, Robert Babuska, János Abonyi, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Stanimir Mollov, Robert Babuška, János Abonyi, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
@@ -35311,7 +35311,7 @@
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radek Sindelár, Robert Babuska </t>
+          <t xml:space="preserve">Radek Sindelár, Robert Babuška </t>
         </is>
       </c>
       <c r="B1164" t="inlineStr">
@@ -35341,7 +35341,7 @@
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
+          <t xml:space="preserve">Jiří Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
@@ -35371,7 +35371,7 @@
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska </t>
+          <t xml:space="preserve">Robert Babuška </t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
@@ -35401,7 +35401,7 @@
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska, Marcel Oosterom </t>
+          <t xml:space="preserve">Robert Babuška, Marcel Oosterom </t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
@@ -35461,7 +35461,7 @@
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Robert Babuška, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
@@ -35581,7 +35581,7 @@
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska, Maurice R. Damen, Chris Hellinga, Henk Maarleveld </t>
+          <t xml:space="preserve">Robert Babuška, Maurice R. Damen, Chris Hellinga, Henk Maarleveld </t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
@@ -35611,7 +35611,7 @@
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samir Mesic, Robert Babuska, Henk C. Hoogsteden, Anton F. M. Verbraak </t>
+          <t xml:space="preserve">Samir Mesic, Robert Babuška, Henk C. Hoogsteden, Anton F. M. Verbraak </t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
@@ -35641,7 +35641,7 @@
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tor Arne Johansen, Robert Babuska </t>
+          <t xml:space="preserve">Tor Arne Johansen, Robert Babuška </t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
@@ -35671,7 +35671,7 @@
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Korba, Robert Babuska, Henk B. Verbruggen, Paul Martin Frank </t>
+          <t xml:space="preserve">Petr Korba, Robert Babuška, Henk B. Verbruggen, Paul Martin Frank </t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
@@ -35701,7 +35701,7 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes A. Roubos, Robert Babuska </t>
+          <t xml:space="preserve">Johannes A. Roubos, Robert Babuška </t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
@@ -35731,7 +35731,7 @@
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska </t>
+          <t xml:space="preserve">Robert Babuška </t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
@@ -35791,7 +35791,7 @@
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
+          <t xml:space="preserve">Jiří Kléma, Jiří Kubalík, Jiří Palous </t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
@@ -35821,7 +35821,7 @@
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska, Peter J. van der Veen, Uzay Kaymak </t>
+          <t xml:space="preserve">Robert Babuška, Peter J. van der Veen, Uzay Kaymak </t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
@@ -35851,7 +35851,7 @@
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandar Ichtev, J. Hellendoom, Robert Babuska, Stanimir Mollov </t>
+          <t xml:space="preserve">Alexandar Ichtev, J. Hellendoom, Robert Babuška, Stanimir Mollov </t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
@@ -35881,7 +35881,7 @@
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
+          <t xml:space="preserve">Jiří Kubalík, Jiří Lazanský, Petr Zikl </t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
@@ -35911,7 +35911,7 @@
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
+          <t xml:space="preserve">Jiří Kubalík, Léon J. M. Rothkrantz, Jiří Lazanský </t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
@@ -35971,7 +35971,7 @@
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stanimir Mollov, Ton J. J. van den Boom, Federico Cuesta, Aníbal Ollero, Robert Babuska </t>
+          <t xml:space="preserve">Stanimir Mollov, Ton J. J. van den Boom, Federico Cuesta, Aníbal Ollero, Robert Babuška </t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
@@ -36001,7 +36001,7 @@
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t xml:space="preserve">János Abonyi, Robert Babuska, Ferenc Szeifert </t>
+          <t xml:space="preserve">János Abonyi, Robert Babuška, Ferenc Szeifert </t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
@@ -36031,7 +36031,7 @@
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Oosterom, Robert Babuska, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Marcel Oosterom, Robert Babuška, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
@@ -36061,7 +36061,7 @@
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fernando Jiménez, Antonio Fernandez Gómez-Skarmeta, Johannes A. Roubos, Robert Babuska </t>
+          <t xml:space="preserve">Fernando Jiménez, Antonio Fernandez Gómez-Skarmeta, Johannes A. Roubos, Robert Babuška </t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
@@ -36091,7 +36091,7 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stanimir Mollov, Peter J. van der Veen, Robert Babuska </t>
+          <t xml:space="preserve">Stanimir Mollov, Peter J. van der Veen, Robert Babuška </t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
@@ -36121,7 +36121,7 @@
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska </t>
+          <t xml:space="preserve">Robert Babuška </t>
         </is>
       </c>
       <c r="B1191" t="inlineStr">
@@ -36151,7 +36151,7 @@
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandar Ichtev, Johannes Hellendoorn, Robert Babuska </t>
+          <t xml:space="preserve">Alexandar Ichtev, Johannes Hellendoorn, Robert Babuška </t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
@@ -36181,7 +36181,7 @@
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stanimir Mollov, Robert Babuska, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Stanimir Mollov, Robert Babuška, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
@@ -36211,7 +36211,7 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Oosterom, Robert Babuska </t>
+          <t xml:space="preserve">Marcel Oosterom, Robert Babuška </t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
@@ -36241,7 +36241,7 @@
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajoy Kumar Palit, Robert Babuska </t>
+          <t xml:space="preserve">Ajoy Kumar Palit, Robert Babuška </t>
         </is>
       </c>
       <c r="B1195" t="inlineStr">
@@ -36361,7 +36361,7 @@
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t xml:space="preserve">János Abonyi, Robert Babuska, Ferenc Szeifert </t>
+          <t xml:space="preserve">János Abonyi, Robert Babuška, Ferenc Szeifert </t>
         </is>
       </c>
       <c r="B1199" t="inlineStr">
@@ -36391,7 +36391,7 @@
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magne Setnes, Robert Babuska </t>
+          <t xml:space="preserve">Magne Setnes, Robert Babuška </t>
         </is>
       </c>
       <c r="B1200" t="inlineStr">
@@ -36511,7 +36511,7 @@
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Oosterom, Robert Babuska </t>
+          <t xml:space="preserve">Marcel Oosterom, Robert Babuška </t>
         </is>
       </c>
       <c r="B1204" t="inlineStr">
@@ -36541,7 +36541,7 @@
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlos Pereira, António Dourado, Robert Babuska </t>
+          <t xml:space="preserve">Carlos Pereira, António Dourado, Robert Babuška </t>
         </is>
       </c>
       <c r="B1205" t="inlineStr">
@@ -36571,7 +36571,7 @@
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t xml:space="preserve">János Abonyi, Robert Babuska </t>
+          <t xml:space="preserve">János Abonyi, Robert Babuška </t>
         </is>
       </c>
       <c r="B1206" t="inlineStr">
@@ -36601,7 +36601,7 @@
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stanimir Mollov, Robert Babuska, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Stanimir Mollov, Robert Babuška, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1207" t="inlineStr">
@@ -36631,7 +36631,7 @@
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t xml:space="preserve">D. Passaquay, M. Bross, Robert Babuska, Serge Boverie, André Titli </t>
+          <t xml:space="preserve">D. Passaquay, M. Bross, Robert Babuška, Serge Boverie, André Titli </t>
         </is>
       </c>
       <c r="B1208" t="inlineStr">
@@ -36691,7 +36691,7 @@
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t xml:space="preserve">János Abonyi, Robert Babuska, Henk B. Verbruggen, Ferenc Szeifert </t>
+          <t xml:space="preserve">János Abonyi, Robert Babuška, Henk B. Verbruggen, Ferenc Szeifert </t>
         </is>
       </c>
       <c r="B1210" t="inlineStr">
@@ -36721,7 +36721,7 @@
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Babuska, J. M. Sousa, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Robert Babuška, J. M. Sousa, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1211" t="inlineStr">
@@ -36751,7 +36751,7 @@
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter J. van der Veen, Robert Babuska, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Peter J. van der Veen, Robert Babuška, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1212" t="inlineStr">
@@ -36811,7 +36811,7 @@
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes A. Roubos, Stanimir Mollov, Robert Babuska, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Johannes A. Roubos, Stanimir Mollov, Robert Babuška, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1214" t="inlineStr">
@@ -36841,7 +36841,7 @@
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magne Setnes, Robert Babuska </t>
+          <t xml:space="preserve">Magne Setnes, Robert Babuška </t>
         </is>
       </c>
       <c r="B1215" t="inlineStr">
@@ -36871,7 +36871,7 @@
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magne Setnes, Robert Babuska, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Magne Setnes, Robert Babuška, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1216" t="inlineStr">
@@ -36901,7 +36901,7 @@
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Péter Baranyi, I. M. Bavelaar, Robert Babuska, László T. Kóczy, André Titli, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Péter Baranyi, I. M. Bavelaar, Robert Babuška, László T. Kóczy, André Titli, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1217" t="inlineStr">
@@ -36931,7 +36931,7 @@
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel P. G. J. Besteman, Camille H. L. Limpens, Robert Babuska, John B. Otten, Michel Verhaegen </t>
+          <t xml:space="preserve">Marcel P. G. J. Besteman, Camille H. L. Limpens, Robert Babuška, John B. Otten, Michel Verhaegen </t>
         </is>
       </c>
       <c r="B1218" t="inlineStr">
@@ -36961,7 +36961,7 @@
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walter M. van Buijtenen, Gerard Schram, Robert Babuska, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Walter M. van Buijtenen, Gerard Schram, Robert Babuška, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1219" t="inlineStr">
@@ -36991,7 +36991,7 @@
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magne Setnes, Robert Babuska, Uzay Kaymak, H. R. van Nauta Lemke </t>
+          <t xml:space="preserve">Magne Setnes, Robert Babuška, Uzay Kaymak, H. R. van Nauta Lemke </t>
         </is>
       </c>
       <c r="B1220" t="inlineStr">
@@ -37021,7 +37021,7 @@
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magne Setnes, Robert Babuska, Henk B. Verbruggen </t>
+          <t xml:space="preserve">Magne Setnes, Robert Babuška, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1221" t="inlineStr">
@@ -37051,7 +37051,7 @@
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. H. den Hartog, Robert Babuska, H. J. R. Deketh, M. Alvarez Grima, P. N. W. Verhoef, Henk B. Verbruggen </t>
+          <t xml:space="preserve">M. H. den Hartog, Robert Babuška, H. J. R. Deketh, M. Alvarez Grima, P. N. W. Verhoef, Henk B. Verbruggen </t>
         </is>
       </c>
       <c r="B1222" t="inlineStr">

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -9289,7 +9289,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2201.10516 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2201.10516 </t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2201.12266 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2201.12266 </t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2202.11908 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2202.11908 </t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.03529 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2102.03529 </t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2102.05126 </t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05547 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2102.05547 </t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.12319 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2102.12319 </t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.13564 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2102.13564 </t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2103.01272 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2103.01272 </t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2103.08245 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2103.08245 </t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2103.09043 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2103.09043 </t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2104.01008 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2104.01008 </t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2104.05207 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2104.05207 </t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2105.13700 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2105.13700 </t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2105.14706 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2105.14706 </t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2106.14195 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2106.14195 </t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2107.06750 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2107.06750 </t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2107.10034 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2107.10034 </t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2108.00415 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2108.00415 </t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2108.01573 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2108.01573 </t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2110.06149 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2110.06149 </t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2001.09705 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2001.09705 </t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2001.10834 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2001.10834 </t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2002.05406 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2002.05406 </t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2003.07916 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2003.07916 </t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2003.09140 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2003.09140 </t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.03340 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2004.03340 </t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.06997 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2004.06997 </t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.08212 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2004.08212 </t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.08858 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2004.08858 </t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.10667 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2004.10667 </t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.11947 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2004.11947 </t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2005.02149 </t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.03586 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2005.03586 </t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.12737 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2005.12737 </t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.13243 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2005.13243 </t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.14664 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2005.14664 </t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2006.12254 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2006.12254 </t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2007.10085 </t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2008.00120 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2008.00120 </t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2008.13503 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2008.13503 </t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2009.01827 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2009.01827 </t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2009.09215 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2009.09215 </t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2010.03920 </t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.10296 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2010.10296 </t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.10903 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2010.10903 </t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2011.12690 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2011.12690 </t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2012.12582 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.2012.12582 </t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1901.00428 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1901.00428 </t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1901.04237 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1901.04237 </t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1901.08335 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1901.08335 </t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1903.02539 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1903.02539 </t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1903.03182 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1903.03182 </t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1903.09688 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1903.09688 </t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1903.11483 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1903.11483 </t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.01677 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1904.01677 </t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08468 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1904.08468 </t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1904.08689 </t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.09193 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1904.09193 </t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.12424 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1904.12424 </t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1905.06782 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1905.06782 </t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1905.07961 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1905.07961 </t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1905.09565 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1905.09565 </t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1905.13100 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1905.13100 </t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1906.08084 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1906.08084 </t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1906.08549 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1906.08549 </t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1907.02594 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1907.02594 </t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1907.08368 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1907.08368 </t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1908.03627 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1908.03627 </t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.04861 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1910.04861 </t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.06241 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1910.06241 </t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1910.07501 </t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.11797 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1910.11797 </t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.01086 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1911.01086 </t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.04873 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1911.04873 </t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1911.10359 </t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
@@ -16069,7 +16069,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.12073 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1911.12073 </t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1912.01525 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1912.01525 </t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1912.02636 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1912.02636 </t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1802.02892 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1802.02892 </t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
@@ -17479,7 +17479,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1802.03375 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1802.03375 </t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
@@ -17509,7 +17509,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1802.04007 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1802.04007 </t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1802.06893 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1802.06893 </t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1804.00595 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1804.00595 </t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1804.00596 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1804.00596 </t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1804.07745 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1804.07745 </t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1805.03107 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1805.03107 </t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1805.06502 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1805.06502 </t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1805.07563 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1805.07563 </t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
@@ -17749,7 +17749,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1806.04774 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1806.04774 </t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1806.07239 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1806.07239 </t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
@@ -17809,7 +17809,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1812.04088 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1812.04088 </t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1812.10860 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1812.10860 </t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1701.08954 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1701.08954 </t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1701.06532 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1701.06532 </t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
@@ -19309,7 +19309,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1704.01071 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1704.01071 </t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1702.00847 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1702.00847 </t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
@@ -19369,7 +19369,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1701.03037 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1701.03037 </t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
@@ -19399,7 +19399,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1703.08864 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1703.08864 </t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1704.03391 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1704.03391 </t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1708.01745 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1708.01745 </t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1710.02198 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1710.02198 </t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1710.10881 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1710.10881 </t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1711.02503 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1711.02503 </t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
@@ -19579,7 +19579,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1712.09405 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1712.09405 </t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1606.04442 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1606.04442 </t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
@@ -21379,7 +21379,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1612.07551 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1612.07551 </t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
@@ -21409,7 +21409,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1611.01328 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1611.01328 </t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1604.08058 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1604.08058 </t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1607.04606 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1607.04606 </t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1605.06996 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1605.06996 </t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1605.09293 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1605.09293 </t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
@@ -21559,7 +21559,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1611.05990 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1611.05990 </t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1606.03888 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1606.03888 </t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1611.08733 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1611.08733 </t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
@@ -21649,7 +21649,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1611.06188 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1611.06188 </t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1612.03651 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1612.03651 </t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1607.01759 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1607.01759 </t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
@@ -21739,7 +21739,7 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1611.09703 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1611.09703 </t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1606.02941 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1606.02941 </t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
@@ -21799,7 +21799,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1608.03350 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1608.03350 </t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
@@ -21829,7 +21829,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1601.05520 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1601.05520 </t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
@@ -21859,7 +21859,7 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1604.08040 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1604.08040 </t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
@@ -21889,7 +21889,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1604.08055 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1604.08055 </t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
@@ -21919,7 +21919,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1502.05698 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1502.05698 </t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
@@ -23629,7 +23629,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1511.06303 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1511.06303 </t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
@@ -23659,7 +23659,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1509.03527 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1509.03527 </t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
@@ -23689,7 +23689,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1509.03534 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1509.03534 </t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
@@ -23719,7 +23719,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1501.02155 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1501.02155 </t>
         </is>
       </c>
       <c r="F777" t="inlineStr">
@@ -23749,7 +23749,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1503.01007 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1503.01007 </t>
         </is>
       </c>
       <c r="F778" t="inlineStr">
@@ -23779,7 +23779,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1412.5335 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1412.5335 </t>
         </is>
       </c>
       <c r="F779" t="inlineStr">
@@ -23809,7 +23809,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1511.08130 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1511.08130 </t>
         </is>
       </c>
       <c r="F780" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1412.7753 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1412.7753 </t>
         </is>
       </c>
       <c r="F781" t="inlineStr">
@@ -23869,7 +23869,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1505.02405 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1505.02405 </t>
         </is>
       </c>
       <c r="F782" t="inlineStr">
@@ -23899,7 +23899,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1512.00408 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1512.00408 </t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1504.02125 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1504.02125 </t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
@@ -23959,7 +23959,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1511.07275 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1511.07275 </t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
@@ -25519,7 +25519,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.1565 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1405.1565 </t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
@@ -25549,7 +25549,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.3906 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1405.3906 </t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -25579,7 +25579,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1409.0553 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1409.0553 </t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
@@ -25609,7 +25609,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1406.7838 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1406.7838 </t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1410.5467 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1410.5467 </t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1402.3578 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1402.3578 </t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1402.2359 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1402.2359 </t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1410.5476 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1410.5476 </t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
@@ -25789,7 +25789,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.3451 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1405.3451 </t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.4053 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1405.4053 </t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
@@ -25849,7 +25849,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1402.3011 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1402.3011 </t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
@@ -25879,7 +25879,7 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1312.5650 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1312.5650 </t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1312.3005 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1312.3005 </t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1310.2491 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1310.2491 </t>
         </is>
       </c>
       <c r="F907" t="inlineStr">
@@ -27649,7 +27649,7 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1309.4962 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1309.4962 </t>
         </is>
       </c>
       <c r="F908" t="inlineStr">
@@ -27679,7 +27679,7 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1310.2797 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1310.2797 </t>
         </is>
       </c>
       <c r="F909" t="inlineStr">
@@ -27709,7 +27709,7 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1310.2805 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1310.2805 </t>
         </is>
       </c>
       <c r="F910" t="inlineStr">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1308.2116 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1308.2116 </t>
         </is>
       </c>
       <c r="F911" t="inlineStr">
@@ -27769,7 +27769,7 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1309.4168 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1309.4168 </t>
         </is>
       </c>
       <c r="F912" t="inlineStr">
@@ -27799,7 +27799,7 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1310.4546 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1310.4546 </t>
         </is>
       </c>
       <c r="F913" t="inlineStr">
@@ -27829,7 +27829,7 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1306.5539 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1306.5539 </t>
         </is>
       </c>
       <c r="F914" t="inlineStr">
@@ -27859,7 +27859,7 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1307.4966 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1307.4966 </t>
         </is>
       </c>
       <c r="F915" t="inlineStr">
@@ -27889,7 +27889,7 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1301.2683 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1301.2683 </t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
@@ -27919,7 +27919,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1301.3781 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1301.3781 </t>
         </is>
       </c>
       <c r="F917" t="inlineStr">
@@ -27949,7 +27949,7 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1304.0897 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1304.0897 </t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
@@ -27979,7 +27979,7 @@
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1305.5710 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1305.5710 </t>
         </is>
       </c>
       <c r="F919" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1204.5094 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1204.5094 </t>
         </is>
       </c>
       <c r="F949" t="inlineStr">
@@ -28909,7 +28909,7 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1206.0141 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1206.0141 </t>
         </is>
       </c>
       <c r="F950" t="inlineStr">
@@ -28939,7 +28939,7 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1206.3460 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1206.3460 </t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
@@ -28969,7 +28969,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1209.3914 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1209.3914 </t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
@@ -28999,7 +28999,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1211.5063 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1211.5063 </t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1211.7012 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1211.7012 </t>
         </is>
       </c>
       <c r="F954" t="inlineStr">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1212.5524 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1212.5524 </t>
         </is>
       </c>
       <c r="F955" t="inlineStr">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1212.5525 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1212.5525 </t>
         </is>
       </c>
       <c r="F956" t="inlineStr">
@@ -30469,7 +30469,7 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1107.3209 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1107.3209 </t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1107.3212 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1107.3212 </t>
         </is>
       </c>
       <c r="F1003" t="inlineStr">
@@ -30529,7 +30529,7 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1108.3446 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1108.3446 </t>
         </is>
       </c>
       <c r="F1004" t="inlineStr">
@@ -30559,7 +30559,7 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1109.0616 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1109.0616 </t>
         </is>
       </c>
       <c r="F1005" t="inlineStr">
@@ -30589,7 +30589,7 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1109.3687 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1109.3687 </t>
         </is>
       </c>
       <c r="F1006" t="inlineStr">
@@ -30619,7 +30619,7 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1112.2313 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1112.2313 </t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1003.6096 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1003.6096 </t>
         </is>
       </c>
       <c r="F1049" t="inlineStr">
@@ -31909,7 +31909,7 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1004.1947 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1004.1947 </t>
         </is>
       </c>
       <c r="F1050" t="inlineStr">
@@ -31939,7 +31939,7 @@
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1005.4552 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1005.4552 </t>
         </is>
       </c>
       <c r="F1051" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1005.4592 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1005.4592 </t>
         </is>
       </c>
       <c r="F1052" t="inlineStr">
@@ -31999,7 +31999,7 @@
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1006.5896 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.1006.5896 </t>
         </is>
       </c>
       <c r="F1053" t="inlineStr">
@@ -32749,7 +32749,7 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/0902.0043 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.0902.0043 </t>
         </is>
       </c>
       <c r="F1078" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/0910.0013 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.0910.0013 </t>
         </is>
       </c>
       <c r="F1079" t="inlineStr">
@@ -32809,7 +32809,7 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/0910.3913 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.0910.3913 </t>
         </is>
       </c>
       <c r="F1080" t="inlineStr">
@@ -35509,7 +35509,7 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/cs/0301026 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/ARXIV.CS/0301026 </t>
         </is>
       </c>
       <c r="F1170" t="inlineStr">
